--- a/Backup/eGP_Monthly_Main_202608.xlsx
+++ b/Backup/eGP_Monthly_Main_202608.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,10 +476,8 @@
           <t>สำนักงบประมาณ</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>0107</t>
-        </is>
+      <c r="C2" t="n">
+        <v>107</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -513,10 +511,8 @@
           <t>กรมสรรพากร</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>0307</t>
-        </is>
+      <c r="C3" t="n">
+        <v>307</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -550,10 +546,8 @@
           <t>กรมชลประทาน</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>0703</t>
-        </is>
+      <c r="C4" t="n">
+        <v>703</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -587,10 +581,8 @@
           <t>กรมการขนส่งทางบก</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>0804</t>
-        </is>
+      <c r="C5" t="n">
+        <v>804</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -624,29 +616,286 @@
           <t>สถาบันพระบรมราชชนก</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" t="n">
+        <v>2117</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างพัฒนาปรับปรุงระบบเครือข่ายคอมพิวเตอร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9bf23c34-d269-445b-bcce-16a496539b75</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>สำนักงานกองทุนสนับสนุนการสร้างเสริมสุขภาพ</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0117</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ประกวดราคาเช่าคอมพิวเตอร์แบบพกพาสำหรับผู้บริหาร ประจำปีงบประมาณ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=baecc251-ef1e-4c38-ac63-95f7f828f511</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>กรมการข้าว</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0718</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การเกษตร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=10b23080-bfc8-42fb-807e-bedc45338efb</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>กรมทางหลวง</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0806</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างโครงการบำรุงรักษาอุปกรณ์จัดเก็บข้อมูล การจราจรทางคอมพิวเตอร์ (Log) กรมทางหลวง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0c7b39eb-ebe6-46f7-abcc-c5af98e4ada0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>สถาบันมาตรวิทยาแห่งชาติ</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1907</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ประกวดราคาเช่างานจ้างเหมาเช่าเครื่องถ่ายเอกสารพร้อมกระดาษ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>★ (กระดาษ)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0f165a93-2faa-4dfa-9393-b3e93c838475</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>กรมส่งเสริมการเรียนรู้</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2033</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อหนังสือส่งเสริมการอ่านสำหรับเด็กและเยาวชนผ่านห้องสมุดประชาชน สกร. ในเขตภาคตะวันออกเฉียงเหนือ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>★ (สมุด)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f5cd6053-8bb5-4643-97f3-109b9542971e</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>สถาบันพระบรมราชชนก</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>2117</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>ประกวดราคาจ้างพัฒนาปรับปรุงระบบเครือข่ายคอมพิวเตอร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>ไม่ระบุ</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>★ (คอมพิวเตอร์)</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9bf23c34-d269-445b-bcce-16a496539b75</t>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อวัสดุสำนักงาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>★ (วัสดุสำนักงาน)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=861277ab-7310-4434-9298-3892a5221830</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>สำนักงานคณะกรรมการอ้อยและน้ำตาลทราย</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2206</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 12 รายการ ประจำปีงบประมาณ พ.ศ. 2569 (งบกองทุนอ้อยฯ) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=af2c1183-0b7f-4ee3-8415-25a1c1a11e21</t>
         </is>
       </c>
     </row>

--- a/Backup/eGP_Monthly_Main_202608.xlsx
+++ b/Backup/eGP_Monthly_Main_202608.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -651,10 +651,8 @@
           <t>สำนักงานกองทุนสนับสนุนการสร้างเสริมสุขภาพ</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>0117</t>
-        </is>
+      <c r="C7" t="n">
+        <v>117</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -688,10 +686,8 @@
           <t>กรมการข้าว</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>0718</t>
-        </is>
+      <c r="C8" t="n">
+        <v>718</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -725,10 +721,8 @@
           <t>กรมทางหลวง</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>0806</t>
-        </is>
+      <c r="C9" t="n">
+        <v>806</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -762,10 +756,8 @@
           <t>สถาบันมาตรวิทยาแห่งชาติ</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1907</t>
-        </is>
+      <c r="C10" t="n">
+        <v>1907</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -799,10 +791,8 @@
           <t>กรมส่งเสริมการเรียนรู้</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2033</t>
-        </is>
+      <c r="C11" t="n">
+        <v>2033</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -836,10 +826,8 @@
           <t>สถาบันพระบรมราชชนก</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>2117</t>
-        </is>
+      <c r="C12" t="n">
+        <v>2117</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -873,27 +861,284 @@
           <t>สำนักงานคณะกรรมการอ้อยและน้ำตาลทราย</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" t="n">
+        <v>2206</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 12 รายการ ประจำปีงบประมาณ พ.ศ. 2569 (งบกองทุนอ้อยฯ) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=af2c1183-0b7f-4ee3-8415-25a1c1a11e21</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>สำนักงานกองทุนสนับสนุนการสร้างเสริมสุขภาพ</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0117</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ประกวดราคาเช่าคอมพิวเตอร์แบบพกพาสำหรับผู้บริหาร ประจำปีงบประมาณ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=baecc251-ef1e-4c38-ac63-95f7f828f511</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>กรมการข้าว</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0718</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การเกษตร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=10b23080-bfc8-42fb-807e-bedc45338efb</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>กรมทางหลวง</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0806</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างโครงการบำรุงรักษาอุปกรณ์จัดเก็บข้อมูล การจราจรทางคอมพิวเตอร์ (Log) กรมทางหลวง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0c7b39eb-ebe6-46f7-abcc-c5af98e4ada0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>สถาบันมาตรวิทยาแห่งชาติ</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1907</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>ประกวดราคาเช่างานจ้างเหมาเช่าเครื่องถ่ายเอกสารพร้อมกระดาษ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>★ (กระดาษ)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0f165a93-2faa-4dfa-9393-b3e93c838475</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>กรมส่งเสริมการเรียนรู้</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2033</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อหนังสือส่งเสริมการอ่านสำหรับเด็กและเยาวชนผ่านห้องสมุดประชาชน สกร. ในเขตภาคตะวันออกเฉียงเหนือ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>★ (สมุด)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f5cd6053-8bb5-4643-97f3-109b9542971e</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>สถาบันพระบรมราชชนก</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2117</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อวัสดุสำนักงาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>★ (วัสดุสำนักงาน)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=861277ab-7310-4434-9298-3892a5221830</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>สำนักงานคณะกรรมการอ้อยและน้ำตาลทราย</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
         <is>
           <t>2206</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 12 รายการ ประจำปีงบประมาณ พ.ศ. 2569 (งบกองทุนอ้อยฯ) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>ไม่ระบุ</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
         <is>
           <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=af2c1183-0b7f-4ee3-8415-25a1c1a11e21</t>
         </is>

--- a/Backup/eGP_Monthly_Main_202608.xlsx
+++ b/Backup/eGP_Monthly_Main_202608.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -888,22 +888,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>สำนักงานกองทุนสนับสนุนการสร้างเสริมสุขภาพ</t>
+          <t>กรมท่าอากาศยาน</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0117</t>
+          <t>0805</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ประกวดราคาเช่าคอมพิวเตอร์แบบพกพาสำหรับผู้บริหาร ประจำปีงบประมาณ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างงานจ้างเหมาทำความสะอาดอาคารที่พักผู้โดยสารรวมทั้งอาคารทำการต่างๆ และเก็บรถเข็นสัมภาระผู้โดยสารที่ท่าอากาศยานพิษณุโลก ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -913,34 +913,34 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (รถเข็น)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=baecc251-ef1e-4c38-ac63-95f7f828f511</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9eae9e6d-5f5d-47dc-b864-fd3d8549a384</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>กรมการข้าว</t>
+          <t>กรมอุทยานแห่งชาติ สัตว์ป่า และพันธุ์พืช</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0718</t>
+          <t>0909</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การเกษตร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์สำรวจ จำนวน 3 รายการ (ครั้งที่ 3) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -955,29 +955,29 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=10b23080-bfc8-42fb-807e-bedc45338efb</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=5dd6888d-2b69-4875-acd3-b146251e20e1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>กรมทางหลวง</t>
+          <t>สำนักงานปลัดกระทรวงดิจิทัลเพื่อเศรษฐกิจและสังคม</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0806</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างโครงการบำรุงรักษาอุปกรณ์จัดเก็บข้อมูล การจราจรทางคอมพิวเตอร์ (Log) กรมทางหลวง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อและติดตั้งจอแสดงผลสำหรับห้องแถลงข่าว และจัดซื้อลำโพงพร้อมอุปกรณ์ต่อพ่วงเพื่อเสริมสร้างภาพลักษณ์และเพิ่มประสิทธิภาพ ในการเผยแพร่ข้อมูลข่าวสารของกระทรวงดิจิทัลเพื่อเศรษฐกิจและสังคม ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -987,34 +987,34 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (จอแสดงผล)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0c7b39eb-ebe6-46f7-abcc-c5af98e4ada0</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=281b104a-8be2-46b2-9841-1a43fbb7f37a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>สถาบันมาตรวิทยาแห่งชาติ</t>
+          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามยาเสพติด</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>1611</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ประกวดราคาเช่างานจ้างเหมาเช่าเครื่องถ่ายเอกสารพร้อมกระดาษ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างก่อสร้างปรับปรุงระบบอากาศแบบแรงดันลบ เครื่องฟอกอากาศพลาสม่า และเครื่องปรับอากาศ อาคารสถาบันวิชาการและตรวจพิสูจน์ยาเสพติด สำนักงาน ป.ป.ส. ทุ่งสองห้อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1024,34 +1024,34 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>★ (กระดาษ)</t>
+          <t>★ (เครื่องปรับอากาศ, เครื่องฟอกอากาศ)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0f165a93-2faa-4dfa-9393-b3e93c838475</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9850738e-1235-4a61-ab2a-d040dc71ad5b</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>กรมส่งเสริมการเรียนรู้</t>
+          <t>สำนักงานประกันสังคม</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>1706</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อหนังสือส่งเสริมการอ่านสำหรับเด็กและเยาวชนผ่านห้องสมุดประชาชน สกร. ในเขตภาคตะวันออกเฉียงเหนือ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุก (ดีเซล) จำนวน 1 คัน   ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1061,34 +1061,34 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>★ (สมุด)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f5cd6053-8bb5-4643-97f3-109b9542971e</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=69728ec3-bdaa-4323-a827-e959c98e24d0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>สถาบันพระบรมราชชนก</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2117</t>
+          <t>2102</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อวัสดุสำนักงาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน ๓ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1098,34 +1098,34 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>★ (วัสดุสำนักงาน)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=861277ab-7310-4434-9298-3892a5221830</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3f346fd2-0db9-4ac6-bd74-ce2a5a956e20</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>สำนักงานคณะกรรมการอ้อยและน้ำตาลทราย</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2206</t>
+          <t>2102</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 12 รายการ ประจำปีงบประมาณ พ.ศ. 2569 (งบกองทุนอ้อยฯ) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน ๓ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1140,7 +1140,44 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=af2c1183-0b7f-4ee3-8415-25a1c1a11e21</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=32757c22-42bc-4800-b794-93897af231b5</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง ประเภทส่วนกลาง (รถไฟฟ้า) จำนวน ๒ คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=bc6205b8-1c14-4f20-9495-1dbaa884298d</t>
         </is>
       </c>
     </row>

--- a/Backup/eGP_Monthly_Main_202608.xlsx
+++ b/Backup/eGP_Monthly_Main_202608.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -896,10 +896,8 @@
           <t>กรมท่าอากาศยาน</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>0805</t>
-        </is>
+      <c r="C14" t="n">
+        <v>805</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -933,10 +931,8 @@
           <t>กรมอุทยานแห่งชาติ สัตว์ป่า และพันธุ์พืช</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>0909</t>
-        </is>
+      <c r="C15" t="n">
+        <v>909</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -970,10 +966,8 @@
           <t>สำนักงานปลัดกระทรวงดิจิทัลเพื่อเศรษฐกิจและสังคม</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>1102</t>
-        </is>
+      <c r="C16" t="n">
+        <v>1102</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1007,10 +1001,8 @@
           <t>สำนักงานคณะกรรมการป้องกันและปราบปรามยาเสพติด</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>1611</t>
-        </is>
+      <c r="C17" t="n">
+        <v>1611</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1044,10 +1036,8 @@
           <t>สำนักงานประกันสังคม</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>1706</t>
-        </is>
+      <c r="C18" t="n">
+        <v>1706</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1081,10 +1071,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C19" t="n">
+        <v>2102</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1118,10 +1106,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C20" t="n">
+        <v>2102</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1155,27 +1141,321 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" t="n">
+        <v>2102</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง ประเภทส่วนกลาง (รถไฟฟ้า) จำนวน ๒ คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=bc6205b8-1c14-4f20-9495-1dbaa884298d</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>กรมท่าอากาศยาน</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างงานจ้างเหมาทำความสะอาดอาคารที่พักผู้โดยสารรวมทั้งอาคารทำการต่างๆ และเก็บรถเข็นสัมภาระผู้โดยสารที่ท่าอากาศยานพิษณุโลก ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>★ (รถเข็น)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9eae9e6d-5f5d-47dc-b864-fd3d8549a384</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>กรมอุทยานแห่งชาติ สัตว์ป่า และพันธุ์พืช</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0909</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์สำรวจ จำนวน 3 รายการ (ครั้งที่ 3) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=5dd6888d-2b69-4875-acd3-b146251e20e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงดิจิทัลเพื่อเศรษฐกิจและสังคม</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อและติดตั้งจอแสดงผลสำหรับห้องแถลงข่าว และจัดซื้อลำโพงพร้อมอุปกรณ์ต่อพ่วงเพื่อเสริมสร้างภาพลักษณ์และเพิ่มประสิทธิภาพ ในการเผยแพร่ข้อมูลข่าวสารของกระทรวงดิจิทัลเพื่อเศรษฐกิจและสังคม ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>★ (จอแสดงผล)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=281b104a-8be2-46b2-9841-1a43fbb7f37a</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามยาเสพติด</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1611</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างก่อสร้างปรับปรุงระบบอากาศแบบแรงดันลบ เครื่องฟอกอากาศพลาสม่า และเครื่องปรับอากาศ อาคารสถาบันวิชาการและตรวจพิสูจน์ยาเสพติด สำนักงาน ป.ป.ส. ทุ่งสองห้อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>★ (เครื่องปรับอากาศ, เครื่องฟอกอากาศ)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9850738e-1235-4a61-ab2a-d040dc71ad5b</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>สำนักงานประกันสังคม</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1706</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุก (ดีเซล) จำนวน 1 คัน   ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=69728ec3-bdaa-4323-a827-e959c98e24d0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
         <is>
           <t>2102</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน ๓ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3f346fd2-0db9-4ac6-bd74-ce2a5a956e20</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน ๓ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=32757c22-42bc-4800-b794-93897af231b5</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
         <is>
           <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง ประเภทส่วนกลาง (รถไฟฟ้า) จำนวน ๒ คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>ไม่ระบุ</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
         <is>
           <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=bc6205b8-1c14-4f20-9495-1dbaa884298d</t>
         </is>

--- a/Backup/eGP_Monthly_Main_202608.xlsx
+++ b/Backup/eGP_Monthly_Main_202608.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1168,22 +1168,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>กรมท่าอากาศยาน</t>
+          <t>กรมสรรพากร</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0805</t>
+          <t>0307</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างงานจ้างเหมาทำความสะอาดอาคารที่พักผู้โดยสารรวมทั้งอาคารทำการต่างๆ และเก็บรถเข็นสัมภาระผู้โดยสารที่ท่าอากาศยานพิษณุโลก ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างโครงการจ้างบำรุงรักษาและซ่อมแซมแก้ไขคอมพิวเตอร์ ซอฟต์แวร์ พร้อมโปรแกรมระบบบัญชีผู้เสียภาษีรายตัว (Taxpayer Account) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1193,34 +1193,34 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>★ (รถเข็น)</t>
+          <t>★ (คอมพิวเตอร์, ซอฟต์แวร์)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9eae9e6d-5f5d-47dc-b864-fd3d8549a384</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d8262e95-f5c5-46b3-b0b4-8df7d9ebaa9b</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>กรมอุทยานแห่งชาติ สัตว์ป่า และพันธุ์พืช</t>
+          <t>กรมชลประทาน</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0909</t>
+          <t>0703</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์สำรวจ จำนวน 3 รายการ (ครั้งที่ 3) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อตู้เหล็ก MDB ขนาด ๒,๑๐๐ x ๒,๑๐๐ x ๖๐๐ mm. และอื่นๆ รวม ๔๕ รายการ พร้อมติดตั้ง สำหรับงานปรับปรุงระบบหม้อแปลงไฟฟ้าและงานระบบไฟฟ้าโครงการห้องควบคุมไฟฟ้า สำนักงานชลประทานที่ ๑๕ ตำบลปากพนังฝั่งตะวันตก อำเภอปากพนัง จังหวัดนครศรีธรรมราช ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1230,34 +1230,34 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (ตู้เหล็ก)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=5dd6888d-2b69-4875-acd3-b146251e20e1</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=923c9a1f-d690-46a9-89d0-aafcacc22c04</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงดิจิทัลเพื่อเศรษฐกิจและสังคม</t>
+          <t>กรมชลประทาน</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>0703</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการจัดซื้อและติดตั้งจอแสดงผลสำหรับห้องแถลงข่าว และจัดซื้อลำโพงพร้อมอุปกรณ์ต่อพ่วงเพื่อเสริมสร้างภาพลักษณ์และเพิ่มประสิทธิภาพ ในการเผยแพร่ข้อมูลข่าวสารของกระทรวงดิจิทัลเพื่อเศรษฐกิจและสังคม ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างงานจัดหาและติดตั้งเครื่องสูบน้ำด้วยไฟฟ้าพลังงานแสงอาทิตย์ชนิดหอยโข่งขับด้วยมอเตอร์ไฟฟ้าอัตราการสูบน้ำ ๐.๐๒ ลูกบาศก์เมตรต่อวินาที ระยะยกน้ำ ๒๕ เมตร และอื่นๆ จำนวน  ๖ รายการ ของโครงการปรับปรุงระบบกระจายน้ำศูนย์พัฒนาการเกษตรภูสิงห์อันเนื่องมาจากพระราชดำริ อำเภอภูสิงห์ จังหวัดศรีสะเกษ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1267,34 +1267,34 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>★ (จอแสดงผล)</t>
+          <t>★ (มอเตอร์)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=281b104a-8be2-46b2-9841-1a43fbb7f37a</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f5c604b0-ce44-45be-9736-9d64de20cb5a</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามยาเสพติด</t>
+          <t>กรมวิชาการเกษตร</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1611</t>
+          <t>0709</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างก่อสร้างปรับปรุงระบบอากาศแบบแรงดันลบ เครื่องฟอกอากาศพลาสม่า และเครื่องปรับอากาศ อาคารสถาบันวิชาการและตรวจพิสูจน์ยาเสพติด สำนักงาน ป.ป.ส. ทุ่งสองห้อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาเคลื่อนย้ายและติดตั้งครุภัณฑ์  จำนวน 58 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1304,34 +1304,34 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>★ (เครื่องปรับอากาศ, เครื่องฟอกอากาศ)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9850738e-1235-4a61-ab2a-d040dc71ad5b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c2bc8af3-277d-4812-8fdc-3225612bc442</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>สำนักงานประกันสังคม</t>
+          <t>กรมการข้าว</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1706</t>
+          <t>0718</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุก (ดีเซล) จำนวน 1 คัน   ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1346,29 +1346,29 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=69728ec3-bdaa-4323-a827-e959c98e24d0</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=89d58d6c-21eb-4b00-ae18-73e2e8debfcd</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กรมทางหลวง</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2102</t>
+          <t>0806</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน ๓ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์สำนักงาน จำนวน 2 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1378,34 +1378,34 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3f346fd2-0db9-4ac6-bd74-ce2a5a956e20</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=16595160-097a-47eb-ad52-50c6ac0669b6</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>องค์การกระจายเสียงและแพร่ภาพสาธารณะแห่งประเทศไทย(ส.ส.ท.)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2102</t>
+          <t>0915</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน ๓ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบริหารโครงการปรับปรุง-ซ่อมแซม เสาส่งสัญญาณโทรทัศน์ จำนวน 3 ต้น (ครั้งที่ 2) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1415,49 +1415,271 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (โทรทัศน์)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=32757c22-42bc-4800-b794-93897af231b5</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d3f92b84-8942-4a5e-8b71-09a3b50f22b8</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
+          <t>กรมการปกครอง</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1503</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อวัสดุสำหรับเครื่องพิมพ์คอมพิวเตอร์ ประจำปีงบประมาณ พ.ศ. 2569 จำนวน 6 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, เครื่องพิมพ์)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=cbd87cdd-c675-49aa-86c1-06701a31d08c</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>2102</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง ประเภทส่วนกลาง (รถไฟฟ้า) จำนวน ๒ คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>ไม่ระบุ</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง  รายการรถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิิ้ลแค็บ จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
         <is>
           <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=bc6205b8-1c14-4f20-9495-1dbaa884298d</t>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3542ee80-4348-403e-9bc6-77eb374130af</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>กรมควบคุมโรค</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อเครื่องคอมพิวเตอร์โน้ตบุ๊ก สำหรับงานประมวลผล จำนวน 35 เครื่อง โดยวิธีประกาศเชิญชวนทั่วไป ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, โน้ตบุ๊ก)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8ef67de6-f58f-45c6-8c3c-a301a465905f</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>กรมวิทยาศาสตร์การแพทย์</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2106</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อน้ำยาสำหรับตรวจคัดกรองทารกแรกเกิดในกลุ่มโรคพันธุกรรมเมตาบอลิก (Inherited Metabolic DisordersIEM) จากกระดาษซับเลือด จำนวน ๓๕ กล่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>★ (กระดาษ)</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9d8080df-2cf1-44d2-8bea-f0761f4fcf27</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>สถาบันพระบรมราชชนก</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2117</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อประกวดราคาซื้อครุภัณฑ์โฆษณาและเผยแพร่ จำนวน 21 รายการ ประจำปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=11c8851e-8e7e-49c2-85f2-94cc884f2e73</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>สถาบันพระบรมราชชนก</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2117</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์คอมพิวเตอร์ขนาดเล็กที่มีมูลค่าไม่เกิน ๕ ล้านบาท ประจำปีงบประมาณ พ.ศ. ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c233d882-7c26-4c1d-9eef-c0205512d68d</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>สำนักงานคณะกรรมการพิเศษเพื่อประสานงานโครงการอันเนื่องมาจากพระราชดำริ</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2504</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างเหมาติดตั้งกล้องโทรทัศน์วงจรปิดสำหรับใช้ในงานรักษา ความปลอดภัยทั่วไปและงานอื่น ๆ บริเวณอาคารโครงการอันเนื่องมาจากพระราชดำริ ประจำปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>★ (โทรทัศน์)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6ce2f91f-a687-49d1-bebb-fc4647123ff8</t>
         </is>
       </c>
     </row>

--- a/Backup/eGP_Monthly_Main_202608.xlsx
+++ b/Backup/eGP_Monthly_Main_202608.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1176,10 +1176,8 @@
           <t>กรมสรรพากร</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>0307</t>
-        </is>
+      <c r="C22" t="n">
+        <v>307</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1213,10 +1211,8 @@
           <t>กรมชลประทาน</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>0703</t>
-        </is>
+      <c r="C23" t="n">
+        <v>703</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1250,10 +1246,8 @@
           <t>กรมชลประทาน</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>0703</t>
-        </is>
+      <c r="C24" t="n">
+        <v>703</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1287,10 +1281,8 @@
           <t>กรมวิชาการเกษตร</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>0709</t>
-        </is>
+      <c r="C25" t="n">
+        <v>709</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1324,10 +1316,8 @@
           <t>กรมการข้าว</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>0718</t>
-        </is>
+      <c r="C26" t="n">
+        <v>718</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1361,10 +1351,8 @@
           <t>กรมทางหลวง</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>0806</t>
-        </is>
+      <c r="C27" t="n">
+        <v>806</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1398,10 +1386,8 @@
           <t>องค์การกระจายเสียงและแพร่ภาพสาธารณะแห่งประเทศไทย(ส.ส.ท.)</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>0915</t>
-        </is>
+      <c r="C28" t="n">
+        <v>915</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1435,10 +1421,8 @@
           <t>กรมการปกครอง</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>1503</t>
-        </is>
+      <c r="C29" t="n">
+        <v>1503</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1472,10 +1456,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C30" t="n">
+        <v>2102</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1509,10 +1491,8 @@
           <t>กรมควบคุมโรค</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>2104</t>
-        </is>
+      <c r="C31" t="n">
+        <v>2104</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1546,10 +1526,8 @@
           <t>กรมวิทยาศาสตร์การแพทย์</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>2106</t>
-        </is>
+      <c r="C32" t="n">
+        <v>2106</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1583,10 +1561,8 @@
           <t>สถาบันพระบรมราชชนก</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>2117</t>
-        </is>
+      <c r="C33" t="n">
+        <v>2117</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1620,10 +1596,8 @@
           <t>สถาบันพระบรมราชชนก</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>2117</t>
-        </is>
+      <c r="C34" t="n">
+        <v>2117</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1657,10 +1631,8 @@
           <t>สำนักงานคณะกรรมการพิเศษเพื่อประสานงานโครงการอันเนื่องมาจากพระราชดำริ</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>2504</t>
-        </is>
+      <c r="C35" t="n">
+        <v>2504</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1680,6 +1652,302 @@
       <c r="G35" t="inlineStr">
         <is>
           <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6ce2f91f-a687-49d1-bebb-fc4647123ff8</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>สำนักงานกองทุนสนับสนุนการสร้างเสริมสุขภาพ</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>0117</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อระบบป้องกันและตรวจจับภัยคุกคามบนเครื่องคอมพิวเตอร์ (Endpoint Detection and Response EDR) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1c672e2a-4730-48d3-bcc5-6ffdfd7ae5e6</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>กรมสรรพสามิต</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>0306</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อโครงการซื้อผงหมึกสำหรับใช้กับเครื่องพิมพ์คอมพิวเตอร์แบบเลเซอร์ ชนิดสี จำนวน ๔ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, เครื่องพิมพ์)</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e98eb1c6-980c-4595-871a-1897574b2734</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>กรมวิชาการเกษตร</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>0709</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างเหมาเคลื่อนย้ายและติดตั้งครุภัณฑ์  จำนวน 58 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4bdd5427-3392-4059-816e-a14011b5c2c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>กรมที่ดิน</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1505</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์พร้อมอุปกรณ์ จำนวน ๑๑ รายการ สำหรับใช้ในราชการหน่วยงานต่าง ๆ รวม ๓ แห่ง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=78f7da52-221c-49ba-aabe-eb85e9677acd</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>กรมที่ดิน</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1505</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างพิมพ์แบบพิมพ์ใบเสร็จรับเงินค่าธรรมเนียมฯ ชนิดใช้กับเครื่องคอมพิวเตอร์ จำนวน ๑๒,๐๐๐,๐๐๐ ชุด (๑๒,๐๐๐ กล่อง) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6e2f2cd5-d34f-496a-b061-5311fba83a12</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์ทันตกรรม จำนวน ๖ รายการ รพ.สต.บางพูด ปีงบประมาณ ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4537f82a-c1fd-4f34-b3aa-edbfc090fe7f</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อรถยนต์ไฟฟ้าประเภทผสมหรือไฮบริด (HEV)ปริมาตรกระบอกสูบไม่เกิน 2,000 ซีซี หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 60 กิโลวัตต์ และกำลังมอเตอร์ไฟฟ้าสูงสุดไม่เกิน 115 กิโลวัตต์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>★ (มอเตอร์)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=636c511e-19c5-419f-857a-d7a3b2ee7266</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>ประกวดราคาเช่าเครื่องคอมพิวเตอร์สำหรับงานสำนักงานและเครื่องคอมพิวเตอร์สำหรับงานประมวลผล จำนวน ๒ รายการ ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=bfa365d5-c79f-471b-9719-ebef768e86ed</t>
         </is>
       </c>
     </row>

--- a/Backup/eGP_Monthly_Main_202608.xlsx
+++ b/Backup/eGP_Monthly_Main_202608.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1278,15 +1278,15 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>กรมวิชาการเกษตร</t>
+          <t>กรมการข้าว</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>709</v>
+        <v>718</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาเคลื่อนย้ายและติดตั้งครุภัณฑ์  จำนวน 58 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c2bc8af3-277d-4812-8fdc-3225612bc442</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=89d58d6c-21eb-4b00-ae18-73e2e8debfcd</t>
         </is>
       </c>
     </row>
@@ -1313,15 +1313,15 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>กรมการข้าว</t>
+          <t>กรมทางหลวง</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>718</v>
+        <v>806</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์สำนักงาน จำนวน 2 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1331,12 +1331,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=89d58d6c-21eb-4b00-ae18-73e2e8debfcd</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=16595160-097a-47eb-ad52-50c6ac0669b6</t>
         </is>
       </c>
     </row>
@@ -1348,15 +1348,15 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>กรมทางหลวง</t>
+          <t>องค์การกระจายเสียงและแพร่ภาพสาธารณะแห่งประเทศไทย(ส.ส.ท.)</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>806</v>
+        <v>915</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์สำนักงาน จำนวน 2 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบริหารโครงการปรับปรุง-ซ่อมแซม เสาส่งสัญญาณโทรทัศน์ จำนวน 3 ต้น (ครั้งที่ 2) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1366,12 +1366,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
+          <t>★ (โทรทัศน์)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=16595160-097a-47eb-ad52-50c6ac0669b6</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d3f92b84-8942-4a5e-8b71-09a3b50f22b8</t>
         </is>
       </c>
     </row>
@@ -1383,15 +1383,15 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>องค์การกระจายเสียงและแพร่ภาพสาธารณะแห่งประเทศไทย(ส.ส.ท.)</t>
+          <t>กรมการปกครอง</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>915</v>
+        <v>1503</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบริหารโครงการปรับปรุง-ซ่อมแซม เสาส่งสัญญาณโทรทัศน์ จำนวน 3 ต้น (ครั้งที่ 2) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อวัสดุสำหรับเครื่องพิมพ์คอมพิวเตอร์ ประจำปีงบประมาณ พ.ศ. 2569 จำนวน 6 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1401,12 +1401,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>★ (โทรทัศน์)</t>
+          <t>★ (คอมพิวเตอร์, เครื่องพิมพ์)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d3f92b84-8942-4a5e-8b71-09a3b50f22b8</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=cbd87cdd-c675-49aa-86c1-06701a31d08c</t>
         </is>
       </c>
     </row>
@@ -1418,15 +1418,15 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>กรมการปกครอง</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1503</v>
+        <v>2102</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อวัสดุสำหรับเครื่องพิมพ์คอมพิวเตอร์ ประจำปีงบประมาณ พ.ศ. 2569 จำนวน 6 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง  รายการรถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิิ้ลแค็บ จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1436,12 +1436,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, เครื่องพิมพ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=cbd87cdd-c675-49aa-86c1-06701a31d08c</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3542ee80-4348-403e-9bc6-77eb374130af</t>
         </is>
       </c>
     </row>
@@ -1453,15 +1453,15 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กรมควบคุมโรค</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2102</v>
+        <v>2104</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง  รายการรถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิิ้ลแค็บ จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องคอมพิวเตอร์โน้ตบุ๊ก สำหรับงานประมวลผล จำนวน 35 เครื่อง โดยวิธีประกาศเชิญชวนทั่วไป ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1471,12 +1471,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, โน้ตบุ๊ก)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3542ee80-4348-403e-9bc6-77eb374130af</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8ef67de6-f58f-45c6-8c3c-a301a465905f</t>
         </is>
       </c>
     </row>
@@ -1488,15 +1488,15 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>กรมควบคุมโรค</t>
+          <t>กรมวิทยาศาสตร์การแพทย์</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2104</v>
+        <v>2106</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องคอมพิวเตอร์โน้ตบุ๊ก สำหรับงานประมวลผล จำนวน 35 เครื่อง โดยวิธีประกาศเชิญชวนทั่วไป ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อน้ำยาสำหรับตรวจคัดกรองทารกแรกเกิดในกลุ่มโรคพันธุกรรมเมตาบอลิก (Inherited Metabolic DisordersIEM) จากกระดาษซับเลือด จำนวน ๓๕ กล่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1506,12 +1506,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, โน้ตบุ๊ก)</t>
+          <t>★ (กระดาษ)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8ef67de6-f58f-45c6-8c3c-a301a465905f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9d8080df-2cf1-44d2-8bea-f0761f4fcf27</t>
         </is>
       </c>
     </row>
@@ -1523,15 +1523,15 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>กรมวิทยาศาสตร์การแพทย์</t>
+          <t>สถาบันพระบรมราชชนก</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2106</v>
+        <v>2117</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อน้ำยาสำหรับตรวจคัดกรองทารกแรกเกิดในกลุ่มโรคพันธุกรรมเมตาบอลิก (Inherited Metabolic DisordersIEM) จากกระดาษซับเลือด จำนวน ๓๕ กล่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อประกวดราคาซื้อครุภัณฑ์โฆษณาและเผยแพร่ จำนวน 21 รายการ ประจำปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>★ (กระดาษ)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9d8080df-2cf1-44d2-8bea-f0761f4fcf27</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=11c8851e-8e7e-49c2-85f2-94cc884f2e73</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อประกวดราคาซื้อครุภัณฑ์โฆษณาและเผยแพร่ จำนวน 21 รายการ ประจำปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์คอมพิวเตอร์ขนาดเล็กที่มีมูลค่าไม่เกิน ๕ ล้านบาท ประจำปีงบประมาณ พ.ศ. ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=11c8851e-8e7e-49c2-85f2-94cc884f2e73</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c233d882-7c26-4c1d-9eef-c0205512d68d</t>
         </is>
       </c>
     </row>
@@ -1593,15 +1593,15 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>สถาบันพระบรมราชชนก</t>
+          <t>สำนักงานคณะกรรมการพิเศษเพื่อประสานงานโครงการอันเนื่องมาจากพระราชดำริ</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2117</v>
+        <v>2504</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์คอมพิวเตอร์ขนาดเล็กที่มีมูลค่าไม่เกิน ๕ ล้านบาท ประจำปีงบประมาณ พ.ศ. ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาติดตั้งกล้องโทรทัศน์วงจรปิดสำหรับใช้ในงานรักษา ความปลอดภัยทั่วไปและงานอื่น ๆ บริเวณอาคารโครงการอันเนื่องมาจากพระราชดำริ ประจำปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1611,32 +1611,32 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (โทรทัศน์)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c233d882-7c26-4c1d-9eef-c0205512d68d</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6ce2f91f-a687-49d1-bebb-fc4647123ff8</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>สำนักงานคณะกรรมการพิเศษเพื่อประสานงานโครงการอันเนื่องมาจากพระราชดำริ</t>
+          <t>สำนักงานกองทุนสนับสนุนการสร้างเสริมสุขภาพ</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2504</v>
+        <v>117</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาติดตั้งกล้องโทรทัศน์วงจรปิดสำหรับใช้ในงานรักษา ความปลอดภัยทั่วไปและงานอื่น ๆ บริเวณอาคารโครงการอันเนื่องมาจากพระราชดำริ ประจำปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อระบบป้องกันและตรวจจับภัยคุกคามบนเครื่องคอมพิวเตอร์ (Endpoint Detection and Response EDR) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1646,12 +1646,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>★ (โทรทัศน์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6ce2f91f-a687-49d1-bebb-fc4647123ff8</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1c672e2a-4730-48d3-bcc5-6ffdfd7ae5e6</t>
         </is>
       </c>
     </row>
@@ -1663,17 +1663,15 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>สำนักงานกองทุนสนับสนุนการสร้างเสริมสุขภาพ</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>0117</t>
-        </is>
+          <t>กรมสรรพสามิต</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>306</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อระบบป้องกันและตรวจจับภัยคุกคามบนเครื่องคอมพิวเตอร์ (Endpoint Detection and Response EDR) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการซื้อผงหมึกสำหรับใช้กับเครื่องพิมพ์คอมพิวเตอร์แบบเลเซอร์ ชนิดสี จำนวน ๔ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1683,12 +1681,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (คอมพิวเตอร์, เครื่องพิมพ์)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1c672e2a-4730-48d3-bcc5-6ffdfd7ae5e6</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e98eb1c6-980c-4595-871a-1897574b2734</t>
         </is>
       </c>
     </row>
@@ -1700,17 +1698,15 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>กรมสรรพสามิต</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>0306</t>
-        </is>
+          <t>กรมวิชาการเกษตร</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>709</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการซื้อผงหมึกสำหรับใช้กับเครื่องพิมพ์คอมพิวเตอร์แบบเลเซอร์ ชนิดสี จำนวน ๔ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาเคลื่อนย้ายและติดตั้งครุภัณฑ์  จำนวน 58 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1720,12 +1716,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, เครื่องพิมพ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e98eb1c6-980c-4595-871a-1897574b2734</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4bdd5427-3392-4059-816e-a14011b5c2c2</t>
         </is>
       </c>
     </row>
@@ -1737,17 +1733,15 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>กรมวิชาการเกษตร</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>0709</t>
-        </is>
+          <t>กรมที่ดิน</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>1505</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาเคลื่อนย้ายและติดตั้งครุภัณฑ์  จำนวน 58 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์พร้อมอุปกรณ์ จำนวน ๑๑ รายการ สำหรับใช้ในราชการหน่วยงานต่าง ๆ รวม ๓ แห่ง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1757,12 +1751,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4bdd5427-3392-4059-816e-a14011b5c2c2</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=78f7da52-221c-49ba-aabe-eb85e9677acd</t>
         </is>
       </c>
     </row>
@@ -1777,14 +1771,12 @@
           <t>กรมที่ดิน</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>1505</t>
-        </is>
+      <c r="C39" t="n">
+        <v>1505</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์พร้อมอุปกรณ์ จำนวน ๑๑ รายการ สำหรับใช้ในราชการหน่วยงานต่าง ๆ รวม ๓ แห่ง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างพิมพ์แบบพิมพ์ใบเสร็จรับเงินค่าธรรมเนียมฯ ชนิดใช้กับเครื่องคอมพิวเตอร์ จำนวน ๑๒,๐๐๐,๐๐๐ ชุด (๑๒,๐๐๐ กล่อง) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1794,12 +1786,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=78f7da52-221c-49ba-aabe-eb85e9677acd</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6e2f2cd5-d34f-496a-b061-5311fba83a12</t>
         </is>
       </c>
     </row>
@@ -1811,17 +1803,15 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>กรมที่ดิน</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>1505</t>
-        </is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>2102</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างพิมพ์แบบพิมพ์ใบเสร็จรับเงินค่าธรรมเนียมฯ ชนิดใช้กับเครื่องคอมพิวเตอร์ จำนวน ๑๒,๐๐๐,๐๐๐ ชุด (๑๒,๐๐๐ กล่อง) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ทันตกรรม จำนวน ๖ รายการ รพ.สต.บางพูด ปีงบประมาณ ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1831,12 +1821,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6e2f2cd5-d34f-496a-b061-5311fba83a12</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4537f82a-c1fd-4f34-b3aa-edbfc090fe7f</t>
         </is>
       </c>
     </row>
@@ -1851,14 +1841,12 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C41" t="n">
+        <v>2102</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ทันตกรรม จำนวน ๖ รายการ รพ.สต.บางพูด ปีงบประมาณ ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อรถยนต์ไฟฟ้าประเภทผสมหรือไฮบริด (HEV)ปริมาตรกระบอกสูบไม่เกิน 2,000 ซีซี หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 60 กิโลวัตต์ และกำลังมอเตอร์ไฟฟ้าสูงสุดไม่เกิน 115 กิโลวัตต์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1868,12 +1856,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (มอเตอร์)</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4537f82a-c1fd-4f34-b3aa-edbfc090fe7f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=636c511e-19c5-419f-857a-d7a3b2ee7266</t>
         </is>
       </c>
     </row>
@@ -1888,14 +1876,12 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C42" t="n">
+        <v>2102</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อรถยนต์ไฟฟ้าประเภทผสมหรือไฮบริด (HEV)ปริมาตรกระบอกสูบไม่เกิน 2,000 ซีซี หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 60 กิโลวัตต์ และกำลังมอเตอร์ไฟฟ้าสูงสุดไม่เกิน 115 กิโลวัตต์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาเช่าเครื่องคอมพิวเตอร์สำหรับงานสำนักงานและเครื่องคอมพิวเตอร์สำหรับงานประมวลผล จำนวน ๒ รายการ ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1905,34 +1891,34 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>★ (มอเตอร์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=636c511e-19c5-419f-857a-d7a3b2ee7266</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=bfa365d5-c79f-471b-9719-ebef768e86ed</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กรมพัฒนาที่ดิน</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2102</t>
+          <t>0708</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ประกวดราคาเช่าเครื่องคอมพิวเตอร์สำหรับงานสำนักงานและเครื่องคอมพิวเตอร์สำหรับงานประมวลผล จำนวน ๒ รายการ ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถกอล์ฟไฟฟ้า ขนาด ๒๓ ที่นั่ง จำนวน ๑ คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1942,12 +1928,123 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ec98788a-c085-48e5-9170-fc39dcb3b80e</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>กรมท่าอากาศยาน</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างงานจ้างเหมาทำความสะอาดอาคารที่พักผู้โดยสาร รวมทั้งอาคารทำการต่างๆ และเก็บรถเข็นสัมภาระผู้โดยสาร ที่ท่าอากาศยานนครศรีธรรมราช ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>★ (รถเข็น)</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=df9a63c8-8a11-4af7-90ff-7075e75f6f70</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>กรมการปกครอง</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1503</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>ประกวดราคาเช่าระบบคอมพิวเตอร์และอุปกรณ์ประกอบตามโครงการจัดหาระบบคอมพิวเตอร์เพื่อให้บริการประชาชนทางด้านทะเบียนและบัตรประจำตัวประชาชน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
           <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=bfa365d5-c79f-471b-9719-ebef768e86ed</t>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=aaa01898-82c5-4979-98ad-3b924e56fa5e</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>กรมสนับสนุนบริการสุขภาพ</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2107</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุกไฟฟ้า ประเภทแบตเตอรี่ (BEV) จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7942968c-7119-4de3-89a6-67f0c3219a77</t>
         </is>
       </c>
     </row>

--- a/Backup/eGP_Monthly_Main_202608.xlsx
+++ b/Backup/eGP_Monthly_Main_202608.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1911,10 +1911,8 @@
           <t>กรมพัฒนาที่ดิน</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>0708</t>
-        </is>
+      <c r="C43" t="n">
+        <v>708</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -1948,10 +1946,8 @@
           <t>กรมท่าอากาศยาน</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>0805</t>
-        </is>
+      <c r="C44" t="n">
+        <v>805</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -1985,10 +1981,8 @@
           <t>กรมการปกครอง</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>1503</t>
-        </is>
+      <c r="C45" t="n">
+        <v>1503</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -2022,10 +2016,8 @@
           <t>กรมสนับสนุนบริการสุขภาพ</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>2107</t>
-        </is>
+      <c r="C46" t="n">
+        <v>2107</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -2045,6 +2037,413 @@
       <c r="G46" t="inlineStr">
         <is>
           <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7942968c-7119-4de3-89a6-67f0c3219a77</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ศูนย์อำนวยการรักษาผลประโยชน์ของชาติทางทะเล</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0138</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อเครื่องคอมพิวเตอร์ สำนักงาน จำนวน ๖๑ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c5565b35-992b-42db-9382-5cd4d0a93a45</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>กองบัญชาการกองทัพไทย</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0208</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อจัดซื้อชิ้นส่วนซ่อมบำรุง, เครื่องมือสำรองทดแทน, เครื่องมือซ่อมบำรุงและสิ่งอำนวยความสะดวกระบบคอมพิวเตอร์และเครือข่าย ตามโครงการส่งกำลังและซ่อมบำรุง กรมการสื่อสารทหาร กองบัญชาการกองทัพไทย  ระยะที่ 2 ประจำปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f32d0c06-300a-4490-942d-2675ad77b846</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>สำนักงานพิพิธภัณฑ์เกษตรเฉลิมพระเกียรติพระบาทสมเด็จพระเจ้าอยู่หัว (องค์การมหาชน)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0719</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อระบบเครื่องปรับอากาศแบบชิลเลอร์ พร้อมติดตั้ง ตำบลคลองหนึ่ง อำเภอคลองหลวง จังหวัดปทุมธานี 1 งาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>★ (เครื่องปรับอากาศ)</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f199228b-fa95-4f46-bc8d-7d292acae98f</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>กรมท่าอากาศยาน</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างเหมาทำความสะอาดอาคารที่พักผู้โดยสาร รวมทั้งอาคารทำการต่าง ๆ และเก็บรถเข็นสัมภาระผู้โดยสาร ที่ท่าอากาศยานน่านนคร ประจำปีงบประมาณ 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>★ (รถเข็น)</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=651d40b6-b435-41c6-8873-70362ee1f386</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>กรมทางหลวง</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0806</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 8 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1b7a05b0-a0f5-4072-9eba-b67d1bbfac34</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>กรมทางหลวง</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0806</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างก่อสร้างงานป้ายจราจร (Road Sign) ชนิดป้ายเตือนความเร็วระบบตรวจวัดอัตโนมัติ (Your Speed Sign) ตามแบบแขวงทางหลวงพิเศษระหว่างเมือง ทางหลวงพิเศษหมายเลข ๙ ตอน บางปะอิน - บางพลี ที่ กม.๗+๒๐๐ - กม.๓๖+๒๐๐ LT., RT. (เป็นช่วง ๆ) ปริมาณงาน ๑๘.๐๐ ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>★ (ป้ายเตือน)</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ef72a1b7-8bcd-48ac-b53d-2c18897908fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>กรมทางหลวง</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>0806</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างก่อสร้างงานป้ายจราจร (Road Sign) ชนิดป้ายเตือนความเร็วระบบตรวจวัดอัตโนมัติ (Your Speed Sign) ตามแบบแขวงทางหลวงพิเศษระหว่างเมือง ทางหลวงพิเศษหมายเลข ๗ ตอน หนองข้างคอก - ตะเคียนเตี้ย กม.๗๘+๑๐๐ - กม.๙๔+๕๐๐ LT., RT. (เป็นช่วง ๆ) ปริมาณงาน ๑๘.๐๐ ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>★ (ป้ายเตือน)</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6c76342a-837c-438f-afb8-73a77b63f5d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>กรมทางหลวง</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>0806</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างก่อสร้างงานป้ายจราจร (Road Sign) ชนิดป้ายเตือนความเร็วระบบตรวจวัดอัตโนมัติ (Your Speed Sign) ตามแบบแขวงทางหลวงพิเศษระหว่างเมือง ทางหลวงพิเศษหมายเลข ๗ ตอน แขวงคลองสองต้นนุ่น - ตะเคียนเตี้ย กม.๑๙+๙๑๐ - กม.๗๘+๑๐๐ LT., RT. (เป็นช่วง ๆ) ปริมาณงาน ๑๗.๐๐ ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>★ (ป้ายเตือน)</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8e26d004-4627-4bfe-b31a-5fbfb958c14d</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>กรมการจัดหางาน</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1703</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์โครงการจัดหาครุภัณฑ์คอมพิวเตอร์สำหรับศูนย์ร่วมบริการช่วยเหลือแรงงานต่างด้าวประจำปีงบประมาณ พ.ศ. ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d4861cb6-80c0-4cc3-9e19-243722109b1c</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>กรมส่งเสริมการเรียนรู้</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2033</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างโครงการการประชาสัมพันธ์การประกวดออกแบบ ห้องสมุดแห่งการอ่าน พลิกโฉมศูนย์การเรียนรู้ตลอดชีวิตประจำจังหวัด (เฟสที่ ๑) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>★ (สมุด)</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a1502f63-3bc7-4991-8c91-3aae4697691f</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>สถาบันพระบรมราชชนก</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2117</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์สำนักงาน ๙ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=62dec7df-5ef3-440a-8894-cdac556ab7e6</t>
         </is>
       </c>
     </row>

--- a/Backup/eGP_Monthly_Main_202608.xlsx
+++ b/Backup/eGP_Monthly_Main_202608.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2051,10 +2051,8 @@
           <t>ศูนย์อำนวยการรักษาผลประโยชน์ของชาติทางทะเล</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>0138</t>
-        </is>
+      <c r="C47" t="n">
+        <v>138</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -2088,10 +2086,8 @@
           <t>กองบัญชาการกองทัพไทย</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>0208</t>
-        </is>
+      <c r="C48" t="n">
+        <v>208</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -2125,10 +2121,8 @@
           <t>สำนักงานพิพิธภัณฑ์เกษตรเฉลิมพระเกียรติพระบาทสมเด็จพระเจ้าอยู่หัว (องค์การมหาชน)</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>0719</t>
-        </is>
+      <c r="C49" t="n">
+        <v>719</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2162,10 +2156,8 @@
           <t>กรมท่าอากาศยาน</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>0805</t>
-        </is>
+      <c r="C50" t="n">
+        <v>805</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2199,10 +2191,8 @@
           <t>กรมทางหลวง</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>0806</t>
-        </is>
+      <c r="C51" t="n">
+        <v>806</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -2236,10 +2226,8 @@
           <t>กรมทางหลวง</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>0806</t>
-        </is>
+      <c r="C52" t="n">
+        <v>806</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -2273,10 +2261,8 @@
           <t>กรมทางหลวง</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>0806</t>
-        </is>
+      <c r="C53" t="n">
+        <v>806</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -2310,10 +2296,8 @@
           <t>กรมทางหลวง</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>0806</t>
-        </is>
+      <c r="C54" t="n">
+        <v>806</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -2347,10 +2331,8 @@
           <t>กรมการจัดหางาน</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>1703</t>
-        </is>
+      <c r="C55" t="n">
+        <v>1703</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -2384,10 +2366,8 @@
           <t>กรมส่งเสริมการเรียนรู้</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>2033</t>
-        </is>
+      <c r="C56" t="n">
+        <v>2033</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -2421,10 +2401,8 @@
           <t>สถาบันพระบรมราชชนก</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>2117</t>
-        </is>
+      <c r="C57" t="n">
+        <v>2117</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -2444,6 +2422,413 @@
       <c r="G57" t="inlineStr">
         <is>
           <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=62dec7df-5ef3-440a-8894-cdac556ab7e6</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>กองทัพบก</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>0204</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อชิ้นส่วนซ่อมคอมพิวเตอร์และอุปกรณ์ประกอบ เเละชิ้นส่วนซ่อมคอมพิวเตอร์ซ่อมเคลื่อนที่ (สนับสนุน บชร.1-4) จำนวน 21 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9288bd0f-8fd4-4029-900a-3e27850eac64</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>กองทัพอากาศ</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>0206</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อเครื่องคอมพิวเตอร์โน้ตบุ๊ก สำหรับงานประมวลผล พร้อมติดตั้ง โปรแกรมระบบปฏิบัติการที่มีลิขสิทธิ์ถูกต้องตามกฎหมาย  จำนวน 14 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, โน้ตบุ๊ก, ระบบปฏิบัติการ)</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c3261ee7-89c8-4302-a803-5214f9dd5652</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>กองบัญชาการกองทัพไทย</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>0208</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อจัดซื้อชิ้นส่วนซ่อมบำรุง, เครื่องมือสำรองทดแทน, เครื่องมือซ่อมบำรุงและสิ่งอำนวยความสะดวกระบบคอมพิวเตอร์และเครือข่าย ตามโครงการส่งกำลังและซ่อมบำรุง กรมการสื่อสารทหาร กองบัญชาการกองทัพไทย  ระยะที่ 2 ประจำปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d02761df-5af1-4901-b0e4-55d84955ca87</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>กรมบัญชีกลาง</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>0304</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อการจัดซื้อผงหมึกเครื่องพิมพ์ จำนวน 6 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>★ (หมึกเครื่องพิมพ์, เครื่องพิมพ์)</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a765d638-98e1-4dd8-a368-7357c6452f7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>กรมท่าอากาศยาน</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างจ้างเหมาทำความสะอาดอาคารที่พักผู้โดยสาร รวมทั้งอาคารทำการต่างๆ และเก็บรถเข็นสัมภาระผู้โดยสาร ที่ท่าอากาศยานอุบลราชธานี ประจำปีงบประมาณ 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>★ (รถเข็น)</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7ce2815f-417a-40f8-98f0-f3ad5fcfb5f4</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>กรมท่าอากาศยาน</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างเหมาทำความสะอาดอาคารที่พักผู้โดยสาร รวมทั้งอาคารทำการต่างๆ และเก็บรถเข็นสัมภาระผู้โดยสาร ที่ท่าอากาศยานระนอง ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>★ (รถเข็น)</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e270c130-86b2-4ca1-b931-b0cdd527deae</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>กรมท่าอากาศยาน</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างเหมาทำความสะอาดอาคารที่พักผู้โดยสาร รวมทั้งอาคารทำการต่างๆ และเก็บรถเข็นสัมภาระผู้โดยสาร ที่ท่าอากาศยานอุดรธานี ประจำปีงบประมาณ ๒๕๗๐ ระยะเวลาจ้าง ๑๒ เดือน ตั้งแต่วันที่ ๑ ตุลาคม ๒๕๖๙ ถึงวันที่ ๓๐ กันยายน ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>★ (รถเข็น)</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c68bceb0-a225-44d1-9f01-2755bf635f6d</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>กรมท่าอากาศยาน</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างงานจ้างเหมาทำความสะอาดอาคารที่พักผู้โดยสาร รวมทั้งอาคารทำการต่าง ๆ และเก็บรถเข็นสัมภาระผู้โดยสาร ที่ท่าอากาศยานสกลนคร ประจำปีงบประมาณ 2570 (เดือน ตุลาคม 2569 - เดือน กันยายน 2570) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>★ (รถเข็น)</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=63c26320-0a57-49c2-b838-a56d90ad3d33</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>กรมการปกครอง</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>1503</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ประกอบอาคารที่ว่าการอำเภอเมืองนครราชสีมา ตำบลในเมือง อำเภอเมืองนครราชสีมา จังหวัดนครราชสีมา ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=185a0dfc-62ed-4497-966a-c01f547f4cfe</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>สำนักงานประกันสังคม</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>1706</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง จำนวน 1 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b01336ca-7547-423f-beb5-e3a81696e22b</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>สำนักงานพัฒนาวิทยาศาสตร์และเทคโนโลยีแห่งชาติ</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>1905</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อระบบครุภัณฑ์สนับสนุนการพัฒนาเศรษฐกิจชีวภาพ เศรษฐกิจหมุนเวียน และเศรษฐกิจสีเขียว ตำบลคลองหนึ่ง อำเภอคลองหลวง จังหวัดปทุมธานี 1 ระบบ เครื่องปั่นเหวี่ยงความเร็วสูง (Superspeed centrifuge) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=359b6f0b-0eeb-4b7f-9d76-b98fb3fa120d</t>
         </is>
       </c>
     </row>

--- a/Backup/eGP_Monthly_Main_202608.xlsx
+++ b/Backup/eGP_Monthly_Main_202608.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G68"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2083,15 +2083,15 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>กองบัญชาการกองทัพไทย</t>
+          <t>สำนักงานพิพิธภัณฑ์เกษตรเฉลิมพระเกียรติพระบาทสมเด็จพระเจ้าอยู่หัว (องค์การมหาชน)</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>208</v>
+        <v>719</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อชิ้นส่วนซ่อมบำรุง, เครื่องมือสำรองทดแทน, เครื่องมือซ่อมบำรุงและสิ่งอำนวยความสะดวกระบบคอมพิวเตอร์และเครือข่าย ตามโครงการส่งกำลังและซ่อมบำรุง กรมการสื่อสารทหาร กองบัญชาการกองทัพไทย  ระยะที่ 2 ประจำปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อระบบเครื่องปรับอากาศแบบชิลเลอร์ พร้อมติดตั้ง ตำบลคลองหนึ่ง อำเภอคลองหลวง จังหวัดปทุมธานี 1 งาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (เครื่องปรับอากาศ)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f32d0c06-300a-4490-942d-2675ad77b846</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f199228b-fa95-4f46-bc8d-7d292acae98f</t>
         </is>
       </c>
     </row>
@@ -2118,15 +2118,15 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>สำนักงานพิพิธภัณฑ์เกษตรเฉลิมพระเกียรติพระบาทสมเด็จพระเจ้าอยู่หัว (องค์การมหาชน)</t>
+          <t>กรมท่าอากาศยาน</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>719</v>
+        <v>805</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อระบบเครื่องปรับอากาศแบบชิลเลอร์ พร้อมติดตั้ง ตำบลคลองหนึ่ง อำเภอคลองหลวง จังหวัดปทุมธานี 1 งาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาทำความสะอาดอาคารที่พักผู้โดยสาร รวมทั้งอาคารทำการต่าง ๆ และเก็บรถเข็นสัมภาระผู้โดยสาร ที่ท่าอากาศยานน่านนคร ประจำปีงบประมาณ 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>★ (เครื่องปรับอากาศ)</t>
+          <t>★ (รถเข็น)</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f199228b-fa95-4f46-bc8d-7d292acae98f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=651d40b6-b435-41c6-8873-70362ee1f386</t>
         </is>
       </c>
     </row>
@@ -2153,15 +2153,15 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>กรมท่าอากาศยาน</t>
+          <t>กรมทางหลวง</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาทำความสะอาดอาคารที่พักผู้โดยสาร รวมทั้งอาคารทำการต่าง ๆ และเก็บรถเข็นสัมภาระผู้โดยสาร ที่ท่าอากาศยานน่านนคร ประจำปีงบประมาณ 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 8 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>★ (รถเข็น)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=651d40b6-b435-41c6-8873-70362ee1f386</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1b7a05b0-a0f5-4072-9eba-b67d1bbfac34</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 8 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างก่อสร้างงานป้ายจราจร (Road Sign) ชนิดป้ายเตือนความเร็วระบบตรวจวัดอัตโนมัติ (Your Speed Sign) ตามแบบแขวงทางหลวงพิเศษระหว่างเมือง ทางหลวงพิเศษหมายเลข ๙ ตอน บางปะอิน - บางพลี ที่ กม.๗+๒๐๐ - กม.๓๖+๒๐๐ LT., RT. (เป็นช่วง ๆ) ปริมาณงาน ๑๘.๐๐ ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2206,12 +2206,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (ป้ายเตือน)</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1b7a05b0-a0f5-4072-9eba-b67d1bbfac34</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ef72a1b7-8bcd-48ac-b53d-2c18897908fc</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างก่อสร้างงานป้ายจราจร (Road Sign) ชนิดป้ายเตือนความเร็วระบบตรวจวัดอัตโนมัติ (Your Speed Sign) ตามแบบแขวงทางหลวงพิเศษระหว่างเมือง ทางหลวงพิเศษหมายเลข ๙ ตอน บางปะอิน - บางพลี ที่ กม.๗+๒๐๐ - กม.๓๖+๒๐๐ LT., RT. (เป็นช่วง ๆ) ปริมาณงาน ๑๘.๐๐ ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างก่อสร้างงานป้ายจราจร (Road Sign) ชนิดป้ายเตือนความเร็วระบบตรวจวัดอัตโนมัติ (Your Speed Sign) ตามแบบแขวงทางหลวงพิเศษระหว่างเมือง ทางหลวงพิเศษหมายเลข ๗ ตอน หนองข้างคอก - ตะเคียนเตี้ย กม.๗๘+๑๐๐ - กม.๙๔+๕๐๐ LT., RT. (เป็นช่วง ๆ) ปริมาณงาน ๑๘.๐๐ ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ef72a1b7-8bcd-48ac-b53d-2c18897908fc</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6c76342a-837c-438f-afb8-73a77b63f5d1</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างก่อสร้างงานป้ายจราจร (Road Sign) ชนิดป้ายเตือนความเร็วระบบตรวจวัดอัตโนมัติ (Your Speed Sign) ตามแบบแขวงทางหลวงพิเศษระหว่างเมือง ทางหลวงพิเศษหมายเลข ๗ ตอน หนองข้างคอก - ตะเคียนเตี้ย กม.๗๘+๑๐๐ - กม.๙๔+๕๐๐ LT., RT. (เป็นช่วง ๆ) ปริมาณงาน ๑๘.๐๐ ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างก่อสร้างงานป้ายจราจร (Road Sign) ชนิดป้ายเตือนความเร็วระบบตรวจวัดอัตโนมัติ (Your Speed Sign) ตามแบบแขวงทางหลวงพิเศษระหว่างเมือง ทางหลวงพิเศษหมายเลข ๗ ตอน แขวงคลองสองต้นนุ่น - ตะเคียนเตี้ย กม.๑๙+๙๑๐ - กม.๗๘+๑๐๐ LT., RT. (เป็นช่วง ๆ) ปริมาณงาน ๑๗.๐๐ ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6c76342a-837c-438f-afb8-73a77b63f5d1</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8e26d004-4627-4bfe-b31a-5fbfb958c14d</t>
         </is>
       </c>
     </row>
@@ -2293,15 +2293,15 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>กรมทางหลวง</t>
+          <t>กรมการจัดหางาน</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>806</v>
+        <v>1703</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างก่อสร้างงานป้ายจราจร (Road Sign) ชนิดป้ายเตือนความเร็วระบบตรวจวัดอัตโนมัติ (Your Speed Sign) ตามแบบแขวงทางหลวงพิเศษระหว่างเมือง ทางหลวงพิเศษหมายเลข ๗ ตอน แขวงคลองสองต้นนุ่น - ตะเคียนเตี้ย กม.๑๙+๙๑๐ - กม.๗๘+๑๐๐ LT., RT. (เป็นช่วง ๆ) ปริมาณงาน ๑๗.๐๐ ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์โครงการจัดหาครุภัณฑ์คอมพิวเตอร์สำหรับศูนย์ร่วมบริการช่วยเหลือแรงงานต่างด้าวประจำปีงบประมาณ พ.ศ. ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2311,12 +2311,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>★ (ป้ายเตือน)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8e26d004-4627-4bfe-b31a-5fbfb958c14d</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d4861cb6-80c0-4cc3-9e19-243722109b1c</t>
         </is>
       </c>
     </row>
@@ -2328,15 +2328,15 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>กรมการจัดหางาน</t>
+          <t>กรมส่งเสริมการเรียนรู้</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1703</v>
+        <v>2033</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์โครงการจัดหาครุภัณฑ์คอมพิวเตอร์สำหรับศูนย์ร่วมบริการช่วยเหลือแรงงานต่างด้าวประจำปีงบประมาณ พ.ศ. ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างโครงการการประชาสัมพันธ์การประกวดออกแบบ ห้องสมุดแห่งการอ่าน พลิกโฉมศูนย์การเรียนรู้ตลอดชีวิตประจำจังหวัด (เฟสที่ ๑) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2346,12 +2346,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (สมุด)</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d4861cb6-80c0-4cc3-9e19-243722109b1c</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a1502f63-3bc7-4991-8c91-3aae4697691f</t>
         </is>
       </c>
     </row>
@@ -2363,15 +2363,15 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>กรมส่งเสริมการเรียนรู้</t>
+          <t>สถาบันพระบรมราชชนก</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>2033</v>
+        <v>2117</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างโครงการการประชาสัมพันธ์การประกวดออกแบบ ห้องสมุดแห่งการอ่าน พลิกโฉมศูนย์การเรียนรู้ตลอดชีวิตประจำจังหวัด (เฟสที่ ๑) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์สำนักงาน ๙ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2381,32 +2381,32 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>★ (สมุด)</t>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a1502f63-3bc7-4991-8c91-3aae4697691f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=62dec7df-5ef3-440a-8894-cdac556ab7e6</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>สถาบันพระบรมราชชนก</t>
+          <t>กองทัพบก</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>2117</v>
+        <v>204</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์สำนักงาน ๙ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อชิ้นส่วนซ่อมคอมพิวเตอร์และอุปกรณ์ประกอบ เเละชิ้นส่วนซ่อมคอมพิวเตอร์ซ่อมเคลื่อนที่ (สนับสนุน บชร.1-4) จำนวน 21 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2416,12 +2416,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=62dec7df-5ef3-440a-8894-cdac556ab7e6</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9288bd0f-8fd4-4029-900a-3e27850eac64</t>
         </is>
       </c>
     </row>
@@ -2433,17 +2433,15 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>กองทัพบก</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>0204</t>
-        </is>
+          <t>กองทัพอากาศ</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>206</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อชิ้นส่วนซ่อมคอมพิวเตอร์และอุปกรณ์ประกอบ เเละชิ้นส่วนซ่อมคอมพิวเตอร์ซ่อมเคลื่อนที่ (สนับสนุน บชร.1-4) จำนวน 21 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องคอมพิวเตอร์โน้ตบุ๊ก สำหรับงานประมวลผล พร้อมติดตั้ง โปรแกรมระบบปฏิบัติการที่มีลิขสิทธิ์ถูกต้องตามกฎหมาย  จำนวน 14 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2453,12 +2451,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (คอมพิวเตอร์, โน้ตบุ๊ก, ระบบปฏิบัติการ)</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9288bd0f-8fd4-4029-900a-3e27850eac64</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c3261ee7-89c8-4302-a803-5214f9dd5652</t>
         </is>
       </c>
     </row>
@@ -2470,17 +2468,15 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>กองทัพอากาศ</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>0206</t>
-        </is>
+          <t>กองบัญชาการกองทัพไทย</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>208</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องคอมพิวเตอร์โน้ตบุ๊ก สำหรับงานประมวลผล พร้อมติดตั้ง โปรแกรมระบบปฏิบัติการที่มีลิขสิทธิ์ถูกต้องตามกฎหมาย  จำนวน 14 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อชิ้นส่วนซ่อมบำรุง, เครื่องมือสำรองทดแทน, เครื่องมือซ่อมบำรุงและสิ่งอำนวยความสะดวกระบบคอมพิวเตอร์และเครือข่าย ตามโครงการส่งกำลังและซ่อมบำรุง กรมการสื่อสารทหาร กองบัญชาการกองทัพไทย  ระยะที่ 2 ประจำปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2490,12 +2486,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, โน้ตบุ๊ก, ระบบปฏิบัติการ)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c3261ee7-89c8-4302-a803-5214f9dd5652</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d02761df-5af1-4901-b0e4-55d84955ca87</t>
         </is>
       </c>
     </row>
@@ -2507,17 +2503,15 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>กองบัญชาการกองทัพไทย</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>0208</t>
-        </is>
+          <t>กรมบัญชีกลาง</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>304</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อชิ้นส่วนซ่อมบำรุง, เครื่องมือสำรองทดแทน, เครื่องมือซ่อมบำรุงและสิ่งอำนวยความสะดวกระบบคอมพิวเตอร์และเครือข่าย ตามโครงการส่งกำลังและซ่อมบำรุง กรมการสื่อสารทหาร กองบัญชาการกองทัพไทย  ระยะที่ 2 ประจำปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อการจัดซื้อผงหมึกเครื่องพิมพ์ จำนวน 6 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2527,12 +2521,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (หมึกเครื่องพิมพ์, เครื่องพิมพ์)</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d02761df-5af1-4901-b0e4-55d84955ca87</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a765d638-98e1-4dd8-a368-7357c6452f7d</t>
         </is>
       </c>
     </row>
@@ -2544,17 +2538,15 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>กรมบัญชีกลาง</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>0304</t>
-        </is>
+          <t>กรมท่าอากาศยาน</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>805</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อการจัดซื้อผงหมึกเครื่องพิมพ์ จำนวน 6 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างจ้างเหมาทำความสะอาดอาคารที่พักผู้โดยสาร รวมทั้งอาคารทำการต่างๆ และเก็บรถเข็นสัมภาระผู้โดยสาร ที่ท่าอากาศยานอุบลราชธานี ประจำปีงบประมาณ 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2564,12 +2556,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>★ (หมึกเครื่องพิมพ์, เครื่องพิมพ์)</t>
+          <t>★ (รถเข็น)</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a765d638-98e1-4dd8-a368-7357c6452f7d</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7ce2815f-417a-40f8-98f0-f3ad5fcfb5f4</t>
         </is>
       </c>
     </row>
@@ -2584,14 +2576,12 @@
           <t>กรมท่าอากาศยาน</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>0805</t>
-        </is>
+      <c r="C62" t="n">
+        <v>805</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างจ้างเหมาทำความสะอาดอาคารที่พักผู้โดยสาร รวมทั้งอาคารทำการต่างๆ และเก็บรถเข็นสัมภาระผู้โดยสาร ที่ท่าอากาศยานอุบลราชธานี ประจำปีงบประมาณ 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาทำความสะอาดอาคารที่พักผู้โดยสาร รวมทั้งอาคารทำการต่างๆ และเก็บรถเข็นสัมภาระผู้โดยสาร ที่ท่าอากาศยานระนอง ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2606,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7ce2815f-417a-40f8-98f0-f3ad5fcfb5f4</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e270c130-86b2-4ca1-b931-b0cdd527deae</t>
         </is>
       </c>
     </row>
@@ -2621,14 +2611,12 @@
           <t>กรมท่าอากาศยาน</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>0805</t>
-        </is>
+      <c r="C63" t="n">
+        <v>805</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาทำความสะอาดอาคารที่พักผู้โดยสาร รวมทั้งอาคารทำการต่างๆ และเก็บรถเข็นสัมภาระผู้โดยสาร ที่ท่าอากาศยานระนอง ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาทำความสะอาดอาคารที่พักผู้โดยสาร รวมทั้งอาคารทำการต่างๆ และเก็บรถเข็นสัมภาระผู้โดยสาร ที่ท่าอากาศยานอุดรธานี ประจำปีงบประมาณ ๒๕๗๐ ระยะเวลาจ้าง ๑๒ เดือน ตั้งแต่วันที่ ๑ ตุลาคม ๒๕๖๙ ถึงวันที่ ๓๐ กันยายน ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2643,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e270c130-86b2-4ca1-b931-b0cdd527deae</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c68bceb0-a225-44d1-9f01-2755bf635f6d</t>
         </is>
       </c>
     </row>
@@ -2658,14 +2646,12 @@
           <t>กรมท่าอากาศยาน</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>0805</t>
-        </is>
+      <c r="C64" t="n">
+        <v>805</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาทำความสะอาดอาคารที่พักผู้โดยสาร รวมทั้งอาคารทำการต่างๆ และเก็บรถเข็นสัมภาระผู้โดยสาร ที่ท่าอากาศยานอุดรธานี ประจำปีงบประมาณ ๒๕๗๐ ระยะเวลาจ้าง ๑๒ เดือน ตั้งแต่วันที่ ๑ ตุลาคม ๒๕๖๙ ถึงวันที่ ๓๐ กันยายน ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างงานจ้างเหมาทำความสะอาดอาคารที่พักผู้โดยสาร รวมทั้งอาคารทำการต่าง ๆ และเก็บรถเข็นสัมภาระผู้โดยสาร ที่ท่าอากาศยานสกลนคร ประจำปีงบประมาณ 2570 (เดือน ตุลาคม 2569 - เดือน กันยายน 2570) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2680,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c68bceb0-a225-44d1-9f01-2755bf635f6d</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=63c26320-0a57-49c2-b838-a56d90ad3d33</t>
         </is>
       </c>
     </row>
@@ -2692,17 +2678,15 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>กรมท่าอากาศยาน</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>0805</t>
-        </is>
+          <t>กรมการปกครอง</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>1503</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างงานจ้างเหมาทำความสะอาดอาคารที่พักผู้โดยสาร รวมทั้งอาคารทำการต่าง ๆ และเก็บรถเข็นสัมภาระผู้โดยสาร ที่ท่าอากาศยานสกลนคร ประจำปีงบประมาณ 2570 (เดือน ตุลาคม 2569 - เดือน กันยายน 2570) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ประกอบอาคารที่ว่าการอำเภอเมืองนครราชสีมา ตำบลในเมือง อำเภอเมืองนครราชสีมา จังหวัดนครราชสีมา ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2712,12 +2696,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>★ (รถเข็น)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=63c26320-0a57-49c2-b838-a56d90ad3d33</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=185a0dfc-62ed-4497-966a-c01f547f4cfe</t>
         </is>
       </c>
     </row>
@@ -2729,17 +2713,15 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>กรมการปกครอง</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>1503</t>
-        </is>
+          <t>สำนักงานประกันสังคม</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>1706</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ประกอบอาคารที่ว่าการอำเภอเมืองนครราชสีมา ตำบลในเมือง อำเภอเมืองนครราชสีมา จังหวัดนครราชสีมา ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง จำนวน 1 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2754,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=185a0dfc-62ed-4497-966a-c01f547f4cfe</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b01336ca-7547-423f-beb5-e3a81696e22b</t>
         </is>
       </c>
     </row>
@@ -2766,17 +2748,15 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>สำนักงานประกันสังคม</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>1706</t>
-        </is>
+          <t>สำนักงานพัฒนาวิทยาศาสตร์และเทคโนโลยีแห่งชาติ</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>1905</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง จำนวน 1 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อระบบครุภัณฑ์สนับสนุนการพัฒนาเศรษฐกิจชีวภาพ เศรษฐกิจหมุนเวียน และเศรษฐกิจสีเขียว ตำบลคลองหนึ่ง อำเภอคลองหลวง จังหวัดปทุมธานี 1 ระบบ เครื่องปั่นเหวี่ยงความเร็วสูง (Superspeed centrifuge) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2791,29 +2771,29 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b01336ca-7547-423f-beb5-e3a81696e22b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=359b6f0b-0eeb-4b7f-9d76-b98fb3fa120d</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>สำนักงานพัฒนาวิทยาศาสตร์และเทคโนโลยีแห่งชาติ</t>
+          <t>ศูนย์อำนวยการรักษาผลประโยชน์ของชาติทางทะเล</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>0138</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อระบบครุภัณฑ์สนับสนุนการพัฒนาเศรษฐกิจชีวภาพ เศรษฐกิจหมุนเวียน และเศรษฐกิจสีเขียว ตำบลคลองหนึ่ง อำเภอคลองหลวง จังหวัดปทุมธานี 1 ระบบ เครื่องปั่นเหวี่ยงความเร็วสูง (Superspeed centrifuge) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องคอมพิวเตอร์โน้ตบุ๊ก สำหรับงานประมวลผล จำนวน ๒๒ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2823,12 +2803,197 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
+          <t>★ (คอมพิวเตอร์, โน้ตบุ๊ก)</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=809976d2-f842-4f28-993b-5dbf2627d012</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงกลาโหม</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>0201</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์แผนกแผนและโครงการ รบท.อท.ศอพท. จำนวน 5 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
           <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=359b6f0b-0eeb-4b7f-9d76-b98fb3fa120d</t>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=24573f9d-aa0a-45b1-91fc-930f70268f4e</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>กรมสรรพากร</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>0307</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อวัสดุสิ้นเปลืองเพื่อใช้กับระบบเครื่องพิมพ์ต่อเนื่องความเร็วสูง เพื่อใช้สำหรับพิมพ์เอกสารทางภาษี ประจำปี พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>★ (เครื่องพิมพ์)</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c848bed5-5bad-40b5-8056-82b6f95bfae2</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>กรมการข้าว</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>0718</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การเกษตร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8218601d-a676-42ae-849d-028704cbe916</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>กรมท่าอากาศยาน</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างงานจ้างเหมาทำความสะอาดอาคารที่พักผู้โดยสาร และเก็บรถเข็นสัมภาระผู้โดยสารที่ท่าอากาศยานลำปาง ประจำปีงบประมาณ ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>★ (รถเข็น)</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=182d87d4-9f00-4361-9f26-bcf65839d3d5</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>กรมโยธาธิการและผังเมือง</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>1507</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างก่อสร้างโครงการก่อสร้างเขื่อนป้องกันตลิ่งริมแม่น้ำยม บ้านวังต้นเกลือ หมู่ที่ 7 ตำบลปากกาง อำเภอลอง จังหวัดแพร่ ความยาวไม่น้อยกว่า 1,000 เมตร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>★ (ปากกา)</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2815a715-ddfc-40d8-b3e8-78d6367955f5</t>
         </is>
       </c>
     </row>

--- a/Backup/eGP_Monthly_Main_202608.xlsx
+++ b/Backup/eGP_Monthly_Main_202608.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,15 +683,15 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>กรมการข้าว</t>
+          <t>กรมทางหลวง</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>718</v>
+        <v>806</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การเกษตร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างโครงการบำรุงรักษาอุปกรณ์จัดเก็บข้อมูล การจราจรทางคอมพิวเตอร์ (Log) กรมทางหลวง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -701,12 +701,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=10b23080-bfc8-42fb-807e-bedc45338efb</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0c7b39eb-ebe6-46f7-abcc-c5af98e4ada0</t>
         </is>
       </c>
     </row>
@@ -718,15 +718,15 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>กรมทางหลวง</t>
+          <t>สถาบันมาตรวิทยาแห่งชาติ</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>806</v>
+        <v>1907</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างโครงการบำรุงรักษาอุปกรณ์จัดเก็บข้อมูล การจราจรทางคอมพิวเตอร์ (Log) กรมทางหลวง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาเช่างานจ้างเหมาเช่าเครื่องถ่ายเอกสารพร้อมกระดาษ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -736,12 +736,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (กระดาษ)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0c7b39eb-ebe6-46f7-abcc-c5af98e4ada0</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0f165a93-2faa-4dfa-9393-b3e93c838475</t>
         </is>
       </c>
     </row>
@@ -753,15 +753,15 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>สถาบันมาตรวิทยาแห่งชาติ</t>
+          <t>กรมส่งเสริมการเรียนรู้</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1907</v>
+        <v>2033</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ประกวดราคาเช่างานจ้างเหมาเช่าเครื่องถ่ายเอกสารพร้อมกระดาษ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อหนังสือส่งเสริมการอ่านสำหรับเด็กและเยาวชนผ่านห้องสมุดประชาชน สกร. ในเขตภาคตะวันออกเฉียงเหนือ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -771,12 +771,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>★ (กระดาษ)</t>
+          <t>★ (สมุด)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0f165a93-2faa-4dfa-9393-b3e93c838475</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f5cd6053-8bb5-4643-97f3-109b9542971e</t>
         </is>
       </c>
     </row>
@@ -788,15 +788,15 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>กรมส่งเสริมการเรียนรู้</t>
+          <t>สถาบันพระบรมราชชนก</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2033</v>
+        <v>2117</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อหนังสือส่งเสริมการอ่านสำหรับเด็กและเยาวชนผ่านห้องสมุดประชาชน สกร. ในเขตภาคตะวันออกเฉียงเหนือ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อวัสดุสำนักงาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -806,12 +806,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>★ (สมุด)</t>
+          <t>★ (วัสดุสำนักงาน)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f5cd6053-8bb5-4643-97f3-109b9542971e</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=861277ab-7310-4434-9298-3892a5221830</t>
         </is>
       </c>
     </row>
@@ -823,15 +823,15 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>สถาบันพระบรมราชชนก</t>
+          <t>สำนักงานคณะกรรมการอ้อยและน้ำตาลทราย</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2117</v>
+        <v>2206</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อวัสดุสำนักงาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 12 รายการ ประจำปีงบประมาณ พ.ศ. 2569 (งบกองทุนอ้อยฯ) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -841,32 +841,32 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>★ (วัสดุสำนักงาน)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=861277ab-7310-4434-9298-3892a5221830</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=af2c1183-0b7f-4ee3-8415-25a1c1a11e21</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>สำนักงานคณะกรรมการอ้อยและน้ำตาลทราย</t>
+          <t>กรมท่าอากาศยาน</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2206</v>
+        <v>805</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 12 รายการ ประจำปีงบประมาณ พ.ศ. 2569 (งบกองทุนอ้อยฯ) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างงานจ้างเหมาทำความสะอาดอาคารที่พักผู้โดยสารรวมทั้งอาคารทำการต่างๆ และเก็บรถเข็นสัมภาระผู้โดยสารที่ท่าอากาศยานพิษณุโลก ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -876,12 +876,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (รถเข็น)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=af2c1183-0b7f-4ee3-8415-25a1c1a11e21</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9eae9e6d-5f5d-47dc-b864-fd3d8549a384</t>
         </is>
       </c>
     </row>
@@ -893,15 +893,15 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>กรมท่าอากาศยาน</t>
+          <t>กรมอุทยานแห่งชาติ สัตว์ป่า และพันธุ์พืช</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>805</v>
+        <v>909</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างงานจ้างเหมาทำความสะอาดอาคารที่พักผู้โดยสารรวมทั้งอาคารทำการต่างๆ และเก็บรถเข็นสัมภาระผู้โดยสารที่ท่าอากาศยานพิษณุโลก ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์สำรวจ จำนวน 3 รายการ (ครั้งที่ 3) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -911,12 +911,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>★ (รถเข็น)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9eae9e6d-5f5d-47dc-b864-fd3d8549a384</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=5dd6888d-2b69-4875-acd3-b146251e20e1</t>
         </is>
       </c>
     </row>
@@ -928,15 +928,15 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>กรมอุทยานแห่งชาติ สัตว์ป่า และพันธุ์พืช</t>
+          <t>สำนักงานปลัดกระทรวงดิจิทัลเพื่อเศรษฐกิจและสังคม</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>909</v>
+        <v>1102</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์สำรวจ จำนวน 3 รายการ (ครั้งที่ 3) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อและติดตั้งจอแสดงผลสำหรับห้องแถลงข่าว และจัดซื้อลำโพงพร้อมอุปกรณ์ต่อพ่วงเพื่อเสริมสร้างภาพลักษณ์และเพิ่มประสิทธิภาพ ในการเผยแพร่ข้อมูลข่าวสารของกระทรวงดิจิทัลเพื่อเศรษฐกิจและสังคม ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -946,12 +946,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (จอแสดงผล)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=5dd6888d-2b69-4875-acd3-b146251e20e1</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=281b104a-8be2-46b2-9841-1a43fbb7f37a</t>
         </is>
       </c>
     </row>
@@ -963,15 +963,15 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงดิจิทัลเพื่อเศรษฐกิจและสังคม</t>
+          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามยาเสพติด</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1102</v>
+        <v>1611</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการจัดซื้อและติดตั้งจอแสดงผลสำหรับห้องแถลงข่าว และจัดซื้อลำโพงพร้อมอุปกรณ์ต่อพ่วงเพื่อเสริมสร้างภาพลักษณ์และเพิ่มประสิทธิภาพ ในการเผยแพร่ข้อมูลข่าวสารของกระทรวงดิจิทัลเพื่อเศรษฐกิจและสังคม ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างก่อสร้างปรับปรุงระบบอากาศแบบแรงดันลบ เครื่องฟอกอากาศพลาสม่า และเครื่องปรับอากาศ อาคารสถาบันวิชาการและตรวจพิสูจน์ยาเสพติด สำนักงาน ป.ป.ส. ทุ่งสองห้อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>★ (จอแสดงผล)</t>
+          <t>★ (เครื่องปรับอากาศ, เครื่องฟอกอากาศ)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=281b104a-8be2-46b2-9841-1a43fbb7f37a</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9850738e-1235-4a61-ab2a-d040dc71ad5b</t>
         </is>
       </c>
     </row>
@@ -998,15 +998,15 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามยาเสพติด</t>
+          <t>สำนักงานประกันสังคม</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1611</v>
+        <v>1706</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างก่อสร้างปรับปรุงระบบอากาศแบบแรงดันลบ เครื่องฟอกอากาศพลาสม่า และเครื่องปรับอากาศ อาคารสถาบันวิชาการและตรวจพิสูจน์ยาเสพติด สำนักงาน ป.ป.ส. ทุ่งสองห้อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุก (ดีเซล) จำนวน 1 คัน   ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1016,12 +1016,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>★ (เครื่องปรับอากาศ, เครื่องฟอกอากาศ)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9850738e-1235-4a61-ab2a-d040dc71ad5b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=69728ec3-bdaa-4323-a827-e959c98e24d0</t>
         </is>
       </c>
     </row>
@@ -1033,15 +1033,15 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>สำนักงานประกันสังคม</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1706</v>
+        <v>2102</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุก (ดีเซล) จำนวน 1 คัน   ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน ๓ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=69728ec3-bdaa-4323-a827-e959c98e24d0</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3f346fd2-0db9-4ac6-bd74-ce2a5a956e20</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน ๓ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน ๓ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3f346fd2-0db9-4ac6-bd74-ce2a5a956e20</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=32757c22-42bc-4800-b794-93897af231b5</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน ๓ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง ประเภทส่วนกลาง (รถไฟฟ้า) จำนวน ๒ คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=32757c22-42bc-4800-b794-93897af231b5</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=bc6205b8-1c14-4f20-9495-1dbaa884298d</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กรมสรรพากร</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2102</v>
+        <v>307</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง ประเภทส่วนกลาง (รถไฟฟ้า) จำนวน ๒ คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างโครงการจ้างบำรุงรักษาและซ่อมแซมแก้ไขคอมพิวเตอร์ ซอฟต์แวร์ พร้อมโปรแกรมระบบบัญชีผู้เสียภาษีรายตัว (Taxpayer Account) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, ซอฟต์แวร์)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=bc6205b8-1c14-4f20-9495-1dbaa884298d</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d8262e95-f5c5-46b3-b0b4-8df7d9ebaa9b</t>
         </is>
       </c>
     </row>
@@ -1173,15 +1173,15 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>กรมสรรพากร</t>
+          <t>กรมชลประทาน</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>307</v>
+        <v>703</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างโครงการจ้างบำรุงรักษาและซ่อมแซมแก้ไขคอมพิวเตอร์ ซอฟต์แวร์ พร้อมโปรแกรมระบบบัญชีผู้เสียภาษีรายตัว (Taxpayer Account) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อตู้เหล็ก MDB ขนาด ๒,๑๐๐ x ๒,๑๐๐ x ๖๐๐ mm. และอื่นๆ รวม ๔๕ รายการ พร้อมติดตั้ง สำหรับงานปรับปรุงระบบหม้อแปลงไฟฟ้าและงานระบบไฟฟ้าโครงการห้องควบคุมไฟฟ้า สำนักงานชลประทานที่ ๑๕ ตำบลปากพนังฝั่งตะวันตก อำเภอปากพนัง จังหวัดนครศรีธรรมราช ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1191,12 +1191,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ซอฟต์แวร์)</t>
+          <t>★ (ตู้เหล็ก)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d8262e95-f5c5-46b3-b0b4-8df7d9ebaa9b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=923c9a1f-d690-46a9-89d0-aafcacc22c04</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อตู้เหล็ก MDB ขนาด ๒,๑๐๐ x ๒,๑๐๐ x ๖๐๐ mm. และอื่นๆ รวม ๔๕ รายการ พร้อมติดตั้ง สำหรับงานปรับปรุงระบบหม้อแปลงไฟฟ้าและงานระบบไฟฟ้าโครงการห้องควบคุมไฟฟ้า สำนักงานชลประทานที่ ๑๕ ตำบลปากพนังฝั่งตะวันตก อำเภอปากพนัง จังหวัดนครศรีธรรมราช ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างงานจัดหาและติดตั้งเครื่องสูบน้ำด้วยไฟฟ้าพลังงานแสงอาทิตย์ชนิดหอยโข่งขับด้วยมอเตอร์ไฟฟ้าอัตราการสูบน้ำ ๐.๐๒ ลูกบาศก์เมตรต่อวินาที ระยะยกน้ำ ๒๕ เมตร และอื่นๆ จำนวน  ๖ รายการ ของโครงการปรับปรุงระบบกระจายน้ำศูนย์พัฒนาการเกษตรภูสิงห์อันเนื่องมาจากพระราชดำริ อำเภอภูสิงห์ จังหวัดศรีสะเกษ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1226,12 +1226,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>★ (ตู้เหล็ก)</t>
+          <t>★ (มอเตอร์)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=923c9a1f-d690-46a9-89d0-aafcacc22c04</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f5c604b0-ce44-45be-9736-9d64de20cb5a</t>
         </is>
       </c>
     </row>
@@ -1243,15 +1243,15 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>กรมชลประทาน</t>
+          <t>กรมการข้าว</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>703</v>
+        <v>718</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างงานจัดหาและติดตั้งเครื่องสูบน้ำด้วยไฟฟ้าพลังงานแสงอาทิตย์ชนิดหอยโข่งขับด้วยมอเตอร์ไฟฟ้าอัตราการสูบน้ำ ๐.๐๒ ลูกบาศก์เมตรต่อวินาที ระยะยกน้ำ ๒๕ เมตร และอื่นๆ จำนวน  ๖ รายการ ของโครงการปรับปรุงระบบกระจายน้ำศูนย์พัฒนาการเกษตรภูสิงห์อันเนื่องมาจากพระราชดำริ อำเภอภูสิงห์ จังหวัดศรีสะเกษ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1261,12 +1261,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>★ (มอเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f5c604b0-ce44-45be-9736-9d64de20cb5a</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=89d58d6c-21eb-4b00-ae18-73e2e8debfcd</t>
         </is>
       </c>
     </row>
@@ -1278,15 +1278,15 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>กรมการข้าว</t>
+          <t>กรมทางหลวง</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>718</v>
+        <v>806</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์สำนักงาน จำนวน 2 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1296,12 +1296,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=89d58d6c-21eb-4b00-ae18-73e2e8debfcd</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=16595160-097a-47eb-ad52-50c6ac0669b6</t>
         </is>
       </c>
     </row>
@@ -1313,15 +1313,15 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>กรมทางหลวง</t>
+          <t>องค์การกระจายเสียงและแพร่ภาพสาธารณะแห่งประเทศไทย(ส.ส.ท.)</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>806</v>
+        <v>915</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์สำนักงาน จำนวน 2 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบริหารโครงการปรับปรุง-ซ่อมแซม เสาส่งสัญญาณโทรทัศน์ จำนวน 3 ต้น (ครั้งที่ 2) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1331,12 +1331,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
+          <t>★ (โทรทัศน์)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=16595160-097a-47eb-ad52-50c6ac0669b6</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d3f92b84-8942-4a5e-8b71-09a3b50f22b8</t>
         </is>
       </c>
     </row>
@@ -1348,15 +1348,15 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>องค์การกระจายเสียงและแพร่ภาพสาธารณะแห่งประเทศไทย(ส.ส.ท.)</t>
+          <t>กรมการปกครอง</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>915</v>
+        <v>1503</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบริหารโครงการปรับปรุง-ซ่อมแซม เสาส่งสัญญาณโทรทัศน์ จำนวน 3 ต้น (ครั้งที่ 2) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อวัสดุสำหรับเครื่องพิมพ์คอมพิวเตอร์ ประจำปีงบประมาณ พ.ศ. 2569 จำนวน 6 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1366,12 +1366,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>★ (โทรทัศน์)</t>
+          <t>★ (คอมพิวเตอร์, เครื่องพิมพ์)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d3f92b84-8942-4a5e-8b71-09a3b50f22b8</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=cbd87cdd-c675-49aa-86c1-06701a31d08c</t>
         </is>
       </c>
     </row>
@@ -1383,15 +1383,15 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>กรมการปกครอง</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1503</v>
+        <v>2102</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อวัสดุสำหรับเครื่องพิมพ์คอมพิวเตอร์ ประจำปีงบประมาณ พ.ศ. 2569 จำนวน 6 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง  รายการรถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิิ้ลแค็บ จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1401,12 +1401,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, เครื่องพิมพ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=cbd87cdd-c675-49aa-86c1-06701a31d08c</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3542ee80-4348-403e-9bc6-77eb374130af</t>
         </is>
       </c>
     </row>
@@ -1418,15 +1418,15 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กรมควบคุมโรค</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2102</v>
+        <v>2104</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง  รายการรถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิิ้ลแค็บ จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องคอมพิวเตอร์โน้ตบุ๊ก สำหรับงานประมวลผล จำนวน 35 เครื่อง โดยวิธีประกาศเชิญชวนทั่วไป ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1436,12 +1436,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, โน้ตบุ๊ก)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3542ee80-4348-403e-9bc6-77eb374130af</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8ef67de6-f58f-45c6-8c3c-a301a465905f</t>
         </is>
       </c>
     </row>
@@ -1453,15 +1453,15 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>กรมควบคุมโรค</t>
+          <t>กรมวิทยาศาสตร์การแพทย์</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2104</v>
+        <v>2106</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องคอมพิวเตอร์โน้ตบุ๊ก สำหรับงานประมวลผล จำนวน 35 เครื่อง โดยวิธีประกาศเชิญชวนทั่วไป ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อน้ำยาสำหรับตรวจคัดกรองทารกแรกเกิดในกลุ่มโรคพันธุกรรมเมตาบอลิก (Inherited Metabolic DisordersIEM) จากกระดาษซับเลือด จำนวน ๓๕ กล่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1471,12 +1471,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, โน้ตบุ๊ก)</t>
+          <t>★ (กระดาษ)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8ef67de6-f58f-45c6-8c3c-a301a465905f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9d8080df-2cf1-44d2-8bea-f0761f4fcf27</t>
         </is>
       </c>
     </row>
@@ -1488,15 +1488,15 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>กรมวิทยาศาสตร์การแพทย์</t>
+          <t>สถาบันพระบรมราชชนก</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2106</v>
+        <v>2117</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อน้ำยาสำหรับตรวจคัดกรองทารกแรกเกิดในกลุ่มโรคพันธุกรรมเมตาบอลิก (Inherited Metabolic DisordersIEM) จากกระดาษซับเลือด จำนวน ๓๕ กล่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อประกวดราคาซื้อครุภัณฑ์โฆษณาและเผยแพร่ จำนวน 21 รายการ ประจำปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1506,12 +1506,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>★ (กระดาษ)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9d8080df-2cf1-44d2-8bea-f0761f4fcf27</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=11c8851e-8e7e-49c2-85f2-94cc884f2e73</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อประกวดราคาซื้อครุภัณฑ์โฆษณาและเผยแพร่ จำนวน 21 รายการ ประจำปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์คอมพิวเตอร์ขนาดเล็กที่มีมูลค่าไม่เกิน ๕ ล้านบาท ประจำปีงบประมาณ พ.ศ. ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=11c8851e-8e7e-49c2-85f2-94cc884f2e73</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c233d882-7c26-4c1d-9eef-c0205512d68d</t>
         </is>
       </c>
     </row>
@@ -1558,15 +1558,15 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>สถาบันพระบรมราชชนก</t>
+          <t>สำนักงานคณะกรรมการพิเศษเพื่อประสานงานโครงการอันเนื่องมาจากพระราชดำริ</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2117</v>
+        <v>2504</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์คอมพิวเตอร์ขนาดเล็กที่มีมูลค่าไม่เกิน ๕ ล้านบาท ประจำปีงบประมาณ พ.ศ. ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาติดตั้งกล้องโทรทัศน์วงจรปิดสำหรับใช้ในงานรักษา ความปลอดภัยทั่วไปและงานอื่น ๆ บริเวณอาคารโครงการอันเนื่องมาจากพระราชดำริ ประจำปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1576,32 +1576,32 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (โทรทัศน์)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c233d882-7c26-4c1d-9eef-c0205512d68d</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6ce2f91f-a687-49d1-bebb-fc4647123ff8</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>สำนักงานคณะกรรมการพิเศษเพื่อประสานงานโครงการอันเนื่องมาจากพระราชดำริ</t>
+          <t>สำนักงานกองทุนสนับสนุนการสร้างเสริมสุขภาพ</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2504</v>
+        <v>117</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาติดตั้งกล้องโทรทัศน์วงจรปิดสำหรับใช้ในงานรักษา ความปลอดภัยทั่วไปและงานอื่น ๆ บริเวณอาคารโครงการอันเนื่องมาจากพระราชดำริ ประจำปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อระบบป้องกันและตรวจจับภัยคุกคามบนเครื่องคอมพิวเตอร์ (Endpoint Detection and Response EDR) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>★ (โทรทัศน์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6ce2f91f-a687-49d1-bebb-fc4647123ff8</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1c672e2a-4730-48d3-bcc5-6ffdfd7ae5e6</t>
         </is>
       </c>
     </row>
@@ -1628,15 +1628,15 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>สำนักงานกองทุนสนับสนุนการสร้างเสริมสุขภาพ</t>
+          <t>กรมสรรพสามิต</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>117</v>
+        <v>306</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อระบบป้องกันและตรวจจับภัยคุกคามบนเครื่องคอมพิวเตอร์ (Endpoint Detection and Response EDR) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการซื้อผงหมึกสำหรับใช้กับเครื่องพิมพ์คอมพิวเตอร์แบบเลเซอร์ ชนิดสี จำนวน ๔ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1646,12 +1646,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (คอมพิวเตอร์, เครื่องพิมพ์)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1c672e2a-4730-48d3-bcc5-6ffdfd7ae5e6</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e98eb1c6-980c-4595-871a-1897574b2734</t>
         </is>
       </c>
     </row>
@@ -1663,15 +1663,15 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>กรมสรรพสามิต</t>
+          <t>กรมวิชาการเกษตร</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>306</v>
+        <v>709</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการซื้อผงหมึกสำหรับใช้กับเครื่องพิมพ์คอมพิวเตอร์แบบเลเซอร์ ชนิดสี จำนวน ๔ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาเคลื่อนย้ายและติดตั้งครุภัณฑ์  จำนวน 58 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1681,12 +1681,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, เครื่องพิมพ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e98eb1c6-980c-4595-871a-1897574b2734</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4bdd5427-3392-4059-816e-a14011b5c2c2</t>
         </is>
       </c>
     </row>
@@ -1698,15 +1698,15 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>กรมวิชาการเกษตร</t>
+          <t>กรมที่ดิน</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>709</v>
+        <v>1505</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาเคลื่อนย้ายและติดตั้งครุภัณฑ์  จำนวน 58 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์พร้อมอุปกรณ์ จำนวน ๑๑ รายการ สำหรับใช้ในราชการหน่วยงานต่าง ๆ รวม ๓ แห่ง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1716,12 +1716,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4bdd5427-3392-4059-816e-a14011b5c2c2</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=78f7da52-221c-49ba-aabe-eb85e9677acd</t>
         </is>
       </c>
     </row>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์พร้อมอุปกรณ์ จำนวน ๑๑ รายการ สำหรับใช้ในราชการหน่วยงานต่าง ๆ รวม ๓ แห่ง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างพิมพ์แบบพิมพ์ใบเสร็จรับเงินค่าธรรมเนียมฯ ชนิดใช้กับเครื่องคอมพิวเตอร์ จำนวน ๑๒,๐๐๐,๐๐๐ ชุด (๑๒,๐๐๐ กล่อง) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1751,12 +1751,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=78f7da52-221c-49ba-aabe-eb85e9677acd</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6e2f2cd5-d34f-496a-b061-5311fba83a12</t>
         </is>
       </c>
     </row>
@@ -1768,15 +1768,15 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>กรมที่ดิน</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1505</v>
+        <v>2102</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างพิมพ์แบบพิมพ์ใบเสร็จรับเงินค่าธรรมเนียมฯ ชนิดใช้กับเครื่องคอมพิวเตอร์ จำนวน ๑๒,๐๐๐,๐๐๐ ชุด (๑๒,๐๐๐ กล่อง) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ทันตกรรม จำนวน ๖ รายการ รพ.สต.บางพูด ปีงบประมาณ ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6e2f2cd5-d34f-496a-b061-5311fba83a12</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4537f82a-c1fd-4f34-b3aa-edbfc090fe7f</t>
         </is>
       </c>
     </row>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ทันตกรรม จำนวน ๖ รายการ รพ.สต.บางพูด ปีงบประมาณ ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อรถยนต์ไฟฟ้าประเภทผสมหรือไฮบริด (HEV)ปริมาตรกระบอกสูบไม่เกิน 2,000 ซีซี หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 60 กิโลวัตต์ และกำลังมอเตอร์ไฟฟ้าสูงสุดไม่เกิน 115 กิโลวัตต์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (มอเตอร์)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4537f82a-c1fd-4f34-b3aa-edbfc090fe7f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=636c511e-19c5-419f-857a-d7a3b2ee7266</t>
         </is>
       </c>
     </row>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อรถยนต์ไฟฟ้าประเภทผสมหรือไฮบริด (HEV)ปริมาตรกระบอกสูบไม่เกิน 2,000 ซีซี หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 60 กิโลวัตต์ และกำลังมอเตอร์ไฟฟ้าสูงสุดไม่เกิน 115 กิโลวัตต์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาเช่าเครื่องคอมพิวเตอร์สำหรับงานสำนักงานและเครื่องคอมพิวเตอร์สำหรับงานประมวลผล จำนวน ๒ รายการ ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1856,32 +1856,32 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>★ (มอเตอร์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=636c511e-19c5-419f-857a-d7a3b2ee7266</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=bfa365d5-c79f-471b-9719-ebef768e86ed</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กรมพัฒนาที่ดิน</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2102</v>
+        <v>708</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ประกวดราคาเช่าเครื่องคอมพิวเตอร์สำหรับงานสำนักงานและเครื่องคอมพิวเตอร์สำหรับงานประมวลผล จำนวน ๒ รายการ ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถกอล์ฟไฟฟ้า ขนาด ๒๓ ที่นั่ง จำนวน ๑ คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1891,12 +1891,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=bfa365d5-c79f-471b-9719-ebef768e86ed</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ec98788a-c085-48e5-9170-fc39dcb3b80e</t>
         </is>
       </c>
     </row>
@@ -1908,15 +1908,15 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>กรมพัฒนาที่ดิน</t>
+          <t>กรมท่าอากาศยาน</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>708</v>
+        <v>805</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถกอล์ฟไฟฟ้า ขนาด ๒๓ ที่นั่ง จำนวน ๑ คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างงานจ้างเหมาทำความสะอาดอาคารที่พักผู้โดยสาร รวมทั้งอาคารทำการต่างๆ และเก็บรถเข็นสัมภาระผู้โดยสาร ที่ท่าอากาศยานนครศรีธรรมราช ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1926,12 +1926,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (รถเข็น)</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ec98788a-c085-48e5-9170-fc39dcb3b80e</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=df9a63c8-8a11-4af7-90ff-7075e75f6f70</t>
         </is>
       </c>
     </row>
@@ -1943,15 +1943,15 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>กรมท่าอากาศยาน</t>
+          <t>กรมการปกครอง</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>805</v>
+        <v>1503</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างงานจ้างเหมาทำความสะอาดอาคารที่พักผู้โดยสาร รวมทั้งอาคารทำการต่างๆ และเก็บรถเข็นสัมภาระผู้โดยสาร ที่ท่าอากาศยานนครศรีธรรมราช ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาเช่าระบบคอมพิวเตอร์และอุปกรณ์ประกอบตามโครงการจัดหาระบบคอมพิวเตอร์เพื่อให้บริการประชาชนทางด้านทะเบียนและบัตรประจำตัวประชาชน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1961,12 +1961,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>★ (รถเข็น)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=df9a63c8-8a11-4af7-90ff-7075e75f6f70</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=aaa01898-82c5-4979-98ad-3b924e56fa5e</t>
         </is>
       </c>
     </row>
@@ -1978,15 +1978,15 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>กรมการปกครอง</t>
+          <t>กรมสนับสนุนบริการสุขภาพ</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1503</v>
+        <v>2107</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ประกวดราคาเช่าระบบคอมพิวเตอร์และอุปกรณ์ประกอบตามโครงการจัดหาระบบคอมพิวเตอร์เพื่อให้บริการประชาชนทางด้านทะเบียนและบัตรประจำตัวประชาชน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุกไฟฟ้า ประเภทแบตเตอรี่ (BEV) จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1996,32 +1996,32 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=aaa01898-82c5-4979-98ad-3b924e56fa5e</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7942968c-7119-4de3-89a6-67f0c3219a77</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>กรมสนับสนุนบริการสุขภาพ</t>
+          <t>ศูนย์อำนวยการรักษาผลประโยชน์ของชาติทางทะเล</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2107</v>
+        <v>138</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุกไฟฟ้า ประเภทแบตเตอรี่ (BEV) จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องคอมพิวเตอร์ สำนักงาน จำนวน ๖๑ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7942968c-7119-4de3-89a6-67f0c3219a77</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c5565b35-992b-42db-9382-5cd4d0a93a45</t>
         </is>
       </c>
     </row>
@@ -2048,15 +2048,15 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ศูนย์อำนวยการรักษาผลประโยชน์ของชาติทางทะเล</t>
+          <t>สำนักงานพิพิธภัณฑ์เกษตรเฉลิมพระเกียรติพระบาทสมเด็จพระเจ้าอยู่หัว (องค์การมหาชน)</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>138</v>
+        <v>719</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องคอมพิวเตอร์ สำนักงาน จำนวน ๖๑ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อระบบเครื่องปรับอากาศแบบชิลเลอร์ พร้อมติดตั้ง ตำบลคลองหนึ่ง อำเภอคลองหลวง จังหวัดปทุมธานี 1 งาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (เครื่องปรับอากาศ)</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c5565b35-992b-42db-9382-5cd4d0a93a45</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f199228b-fa95-4f46-bc8d-7d292acae98f</t>
         </is>
       </c>
     </row>
@@ -2083,15 +2083,15 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>สำนักงานพิพิธภัณฑ์เกษตรเฉลิมพระเกียรติพระบาทสมเด็จพระเจ้าอยู่หัว (องค์การมหาชน)</t>
+          <t>กรมท่าอากาศยาน</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>719</v>
+        <v>805</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อระบบเครื่องปรับอากาศแบบชิลเลอร์ พร้อมติดตั้ง ตำบลคลองหนึ่ง อำเภอคลองหลวง จังหวัดปทุมธานี 1 งาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาทำความสะอาดอาคารที่พักผู้โดยสาร รวมทั้งอาคารทำการต่าง ๆ และเก็บรถเข็นสัมภาระผู้โดยสาร ที่ท่าอากาศยานน่านนคร ประจำปีงบประมาณ 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>★ (เครื่องปรับอากาศ)</t>
+          <t>★ (รถเข็น)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f199228b-fa95-4f46-bc8d-7d292acae98f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=651d40b6-b435-41c6-8873-70362ee1f386</t>
         </is>
       </c>
     </row>
@@ -2118,15 +2118,15 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>กรมท่าอากาศยาน</t>
+          <t>กรมทางหลวง</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาทำความสะอาดอาคารที่พักผู้โดยสาร รวมทั้งอาคารทำการต่าง ๆ และเก็บรถเข็นสัมภาระผู้โดยสาร ที่ท่าอากาศยานน่านนคร ประจำปีงบประมาณ 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 8 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>★ (รถเข็น)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=651d40b6-b435-41c6-8873-70362ee1f386</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1b7a05b0-a0f5-4072-9eba-b67d1bbfac34</t>
         </is>
       </c>
     </row>
@@ -2161,7 +2161,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 8 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างก่อสร้างงานป้ายจราจร (Road Sign) ชนิดป้ายเตือนความเร็วระบบตรวจวัดอัตโนมัติ (Your Speed Sign) ตามแบบแขวงทางหลวงพิเศษระหว่างเมือง ทางหลวงพิเศษหมายเลข ๙ ตอน บางปะอิน - บางพลี ที่ กม.๗+๒๐๐ - กม.๓๖+๒๐๐ LT., RT. (เป็นช่วง ๆ) ปริมาณงาน ๑๘.๐๐ ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (ป้ายเตือน)</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1b7a05b0-a0f5-4072-9eba-b67d1bbfac34</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ef72a1b7-8bcd-48ac-b53d-2c18897908fc</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างก่อสร้างงานป้ายจราจร (Road Sign) ชนิดป้ายเตือนความเร็วระบบตรวจวัดอัตโนมัติ (Your Speed Sign) ตามแบบแขวงทางหลวงพิเศษระหว่างเมือง ทางหลวงพิเศษหมายเลข ๙ ตอน บางปะอิน - บางพลี ที่ กม.๗+๒๐๐ - กม.๓๖+๒๐๐ LT., RT. (เป็นช่วง ๆ) ปริมาณงาน ๑๘.๐๐ ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างก่อสร้างงานป้ายจราจร (Road Sign) ชนิดป้ายเตือนความเร็วระบบตรวจวัดอัตโนมัติ (Your Speed Sign) ตามแบบแขวงทางหลวงพิเศษระหว่างเมือง ทางหลวงพิเศษหมายเลข ๗ ตอน หนองข้างคอก - ตะเคียนเตี้ย กม.๗๘+๑๐๐ - กม.๙๔+๕๐๐ LT., RT. (เป็นช่วง ๆ) ปริมาณงาน ๑๘.๐๐ ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ef72a1b7-8bcd-48ac-b53d-2c18897908fc</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6c76342a-837c-438f-afb8-73a77b63f5d1</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างก่อสร้างงานป้ายจราจร (Road Sign) ชนิดป้ายเตือนความเร็วระบบตรวจวัดอัตโนมัติ (Your Speed Sign) ตามแบบแขวงทางหลวงพิเศษระหว่างเมือง ทางหลวงพิเศษหมายเลข ๗ ตอน หนองข้างคอก - ตะเคียนเตี้ย กม.๗๘+๑๐๐ - กม.๙๔+๕๐๐ LT., RT. (เป็นช่วง ๆ) ปริมาณงาน ๑๘.๐๐ ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างก่อสร้างงานป้ายจราจร (Road Sign) ชนิดป้ายเตือนความเร็วระบบตรวจวัดอัตโนมัติ (Your Speed Sign) ตามแบบแขวงทางหลวงพิเศษระหว่างเมือง ทางหลวงพิเศษหมายเลข ๗ ตอน แขวงคลองสองต้นนุ่น - ตะเคียนเตี้ย กม.๑๙+๙๑๐ - กม.๗๘+๑๐๐ LT., RT. (เป็นช่วง ๆ) ปริมาณงาน ๑๗.๐๐ ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6c76342a-837c-438f-afb8-73a77b63f5d1</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8e26d004-4627-4bfe-b31a-5fbfb958c14d</t>
         </is>
       </c>
     </row>
@@ -2258,15 +2258,15 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>กรมทางหลวง</t>
+          <t>กรมการจัดหางาน</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>806</v>
+        <v>1703</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างก่อสร้างงานป้ายจราจร (Road Sign) ชนิดป้ายเตือนความเร็วระบบตรวจวัดอัตโนมัติ (Your Speed Sign) ตามแบบแขวงทางหลวงพิเศษระหว่างเมือง ทางหลวงพิเศษหมายเลข ๗ ตอน แขวงคลองสองต้นนุ่น - ตะเคียนเตี้ย กม.๑๙+๙๑๐ - กม.๗๘+๑๐๐ LT., RT. (เป็นช่วง ๆ) ปริมาณงาน ๑๗.๐๐ ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์โครงการจัดหาครุภัณฑ์คอมพิวเตอร์สำหรับศูนย์ร่วมบริการช่วยเหลือแรงงานต่างด้าวประจำปีงบประมาณ พ.ศ. ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2276,12 +2276,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>★ (ป้ายเตือน)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8e26d004-4627-4bfe-b31a-5fbfb958c14d</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d4861cb6-80c0-4cc3-9e19-243722109b1c</t>
         </is>
       </c>
     </row>
@@ -2293,15 +2293,15 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>กรมการจัดหางาน</t>
+          <t>กรมส่งเสริมการเรียนรู้</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1703</v>
+        <v>2033</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์โครงการจัดหาครุภัณฑ์คอมพิวเตอร์สำหรับศูนย์ร่วมบริการช่วยเหลือแรงงานต่างด้าวประจำปีงบประมาณ พ.ศ. ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างโครงการการประชาสัมพันธ์การประกวดออกแบบ ห้องสมุดแห่งการอ่าน พลิกโฉมศูนย์การเรียนรู้ตลอดชีวิตประจำจังหวัด (เฟสที่ ๑) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2311,12 +2311,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (สมุด)</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d4861cb6-80c0-4cc3-9e19-243722109b1c</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a1502f63-3bc7-4991-8c91-3aae4697691f</t>
         </is>
       </c>
     </row>
@@ -2328,15 +2328,15 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>กรมส่งเสริมการเรียนรู้</t>
+          <t>สถาบันพระบรมราชชนก</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>2033</v>
+        <v>2117</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างโครงการการประชาสัมพันธ์การประกวดออกแบบ ห้องสมุดแห่งการอ่าน พลิกโฉมศูนย์การเรียนรู้ตลอดชีวิตประจำจังหวัด (เฟสที่ ๑) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์สำนักงาน ๙ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2346,32 +2346,32 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>★ (สมุด)</t>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a1502f63-3bc7-4991-8c91-3aae4697691f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=62dec7df-5ef3-440a-8894-cdac556ab7e6</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>สถาบันพระบรมราชชนก</t>
+          <t>กองทัพบก</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>2117</v>
+        <v>204</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์สำนักงาน ๙ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อชิ้นส่วนซ่อมคอมพิวเตอร์และอุปกรณ์ประกอบ เเละชิ้นส่วนซ่อมคอมพิวเตอร์ซ่อมเคลื่อนที่ (สนับสนุน บชร.1-4) จำนวน 21 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2381,12 +2381,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=62dec7df-5ef3-440a-8894-cdac556ab7e6</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9288bd0f-8fd4-4029-900a-3e27850eac64</t>
         </is>
       </c>
     </row>
@@ -2398,15 +2398,15 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>กองทัพบก</t>
+          <t>กองทัพอากาศ</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อชิ้นส่วนซ่อมคอมพิวเตอร์และอุปกรณ์ประกอบ เเละชิ้นส่วนซ่อมคอมพิวเตอร์ซ่อมเคลื่อนที่ (สนับสนุน บชร.1-4) จำนวน 21 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องคอมพิวเตอร์โน้ตบุ๊ก สำหรับงานประมวลผล พร้อมติดตั้ง โปรแกรมระบบปฏิบัติการที่มีลิขสิทธิ์ถูกต้องตามกฎหมาย  จำนวน 14 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2416,12 +2416,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (คอมพิวเตอร์, โน้ตบุ๊ก, ระบบปฏิบัติการ)</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9288bd0f-8fd4-4029-900a-3e27850eac64</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c3261ee7-89c8-4302-a803-5214f9dd5652</t>
         </is>
       </c>
     </row>
@@ -2433,15 +2433,15 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>กองทัพอากาศ</t>
+          <t>กองบัญชาการกองทัพไทย</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องคอมพิวเตอร์โน้ตบุ๊ก สำหรับงานประมวลผล พร้อมติดตั้ง โปรแกรมระบบปฏิบัติการที่มีลิขสิทธิ์ถูกต้องตามกฎหมาย  จำนวน 14 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อชิ้นส่วนซ่อมบำรุง, เครื่องมือสำรองทดแทน, เครื่องมือซ่อมบำรุงและสิ่งอำนวยความสะดวกระบบคอมพิวเตอร์และเครือข่าย ตามโครงการส่งกำลังและซ่อมบำรุง กรมการสื่อสารทหาร กองบัญชาการกองทัพไทย  ระยะที่ 2 ประจำปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, โน้ตบุ๊ก, ระบบปฏิบัติการ)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c3261ee7-89c8-4302-a803-5214f9dd5652</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d02761df-5af1-4901-b0e4-55d84955ca87</t>
         </is>
       </c>
     </row>
@@ -2468,15 +2468,15 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>กองบัญชาการกองทัพไทย</t>
+          <t>กรมบัญชีกลาง</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>208</v>
+        <v>304</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อชิ้นส่วนซ่อมบำรุง, เครื่องมือสำรองทดแทน, เครื่องมือซ่อมบำรุงและสิ่งอำนวยความสะดวกระบบคอมพิวเตอร์และเครือข่าย ตามโครงการส่งกำลังและซ่อมบำรุง กรมการสื่อสารทหาร กองบัญชาการกองทัพไทย  ระยะที่ 2 ประจำปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อการจัดซื้อผงหมึกเครื่องพิมพ์ จำนวน 6 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (หมึกเครื่องพิมพ์, เครื่องพิมพ์)</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d02761df-5af1-4901-b0e4-55d84955ca87</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a765d638-98e1-4dd8-a368-7357c6452f7d</t>
         </is>
       </c>
     </row>
@@ -2503,15 +2503,15 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>กรมบัญชีกลาง</t>
+          <t>กรมท่าอากาศยาน</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>304</v>
+        <v>805</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อการจัดซื้อผงหมึกเครื่องพิมพ์ จำนวน 6 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างจ้างเหมาทำความสะอาดอาคารที่พักผู้โดยสาร รวมทั้งอาคารทำการต่างๆ และเก็บรถเข็นสัมภาระผู้โดยสาร ที่ท่าอากาศยานอุบลราชธานี ประจำปีงบประมาณ 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>★ (หมึกเครื่องพิมพ์, เครื่องพิมพ์)</t>
+          <t>★ (รถเข็น)</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a765d638-98e1-4dd8-a368-7357c6452f7d</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7ce2815f-417a-40f8-98f0-f3ad5fcfb5f4</t>
         </is>
       </c>
     </row>
@@ -2546,7 +2546,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างจ้างเหมาทำความสะอาดอาคารที่พักผู้โดยสาร รวมทั้งอาคารทำการต่างๆ และเก็บรถเข็นสัมภาระผู้โดยสาร ที่ท่าอากาศยานอุบลราชธานี ประจำปีงบประมาณ 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาทำความสะอาดอาคารที่พักผู้โดยสาร รวมทั้งอาคารทำการต่างๆ และเก็บรถเข็นสัมภาระผู้โดยสาร ที่ท่าอากาศยานระนอง ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7ce2815f-417a-40f8-98f0-f3ad5fcfb5f4</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e270c130-86b2-4ca1-b931-b0cdd527deae</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาทำความสะอาดอาคารที่พักผู้โดยสาร รวมทั้งอาคารทำการต่างๆ และเก็บรถเข็นสัมภาระผู้โดยสาร ที่ท่าอากาศยานระนอง ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาทำความสะอาดอาคารที่พักผู้โดยสาร รวมทั้งอาคารทำการต่างๆ และเก็บรถเข็นสัมภาระผู้โดยสาร ที่ท่าอากาศยานอุดรธานี ประจำปีงบประมาณ ๒๕๗๐ ระยะเวลาจ้าง ๑๒ เดือน ตั้งแต่วันที่ ๑ ตุลาคม ๒๕๖๙ ถึงวันที่ ๓๐ กันยายน ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e270c130-86b2-4ca1-b931-b0cdd527deae</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c68bceb0-a225-44d1-9f01-2755bf635f6d</t>
         </is>
       </c>
     </row>
@@ -2616,7 +2616,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาทำความสะอาดอาคารที่พักผู้โดยสาร รวมทั้งอาคารทำการต่างๆ และเก็บรถเข็นสัมภาระผู้โดยสาร ที่ท่าอากาศยานอุดรธานี ประจำปีงบประมาณ ๒๕๗๐ ระยะเวลาจ้าง ๑๒ เดือน ตั้งแต่วันที่ ๑ ตุลาคม ๒๕๖๙ ถึงวันที่ ๓๐ กันยายน ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างงานจ้างเหมาทำความสะอาดอาคารที่พักผู้โดยสาร รวมทั้งอาคารทำการต่าง ๆ และเก็บรถเข็นสัมภาระผู้โดยสาร ที่ท่าอากาศยานสกลนคร ประจำปีงบประมาณ 2570 (เดือน ตุลาคม 2569 - เดือน กันยายน 2570) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c68bceb0-a225-44d1-9f01-2755bf635f6d</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=63c26320-0a57-49c2-b838-a56d90ad3d33</t>
         </is>
       </c>
     </row>
@@ -2643,15 +2643,15 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>กรมท่าอากาศยาน</t>
+          <t>กรมการปกครอง</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>805</v>
+        <v>1503</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างงานจ้างเหมาทำความสะอาดอาคารที่พักผู้โดยสาร รวมทั้งอาคารทำการต่าง ๆ และเก็บรถเข็นสัมภาระผู้โดยสาร ที่ท่าอากาศยานสกลนคร ประจำปีงบประมาณ 2570 (เดือน ตุลาคม 2569 - เดือน กันยายน 2570) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ประกอบอาคารที่ว่าการอำเภอเมืองนครราชสีมา ตำบลในเมือง อำเภอเมืองนครราชสีมา จังหวัดนครราชสีมา ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2661,12 +2661,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>★ (รถเข็น)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=63c26320-0a57-49c2-b838-a56d90ad3d33</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=185a0dfc-62ed-4497-966a-c01f547f4cfe</t>
         </is>
       </c>
     </row>
@@ -2678,15 +2678,15 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>กรมการปกครอง</t>
+          <t>สำนักงานประกันสังคม</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1503</v>
+        <v>1706</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ประกอบอาคารที่ว่าการอำเภอเมืองนครราชสีมา ตำบลในเมือง อำเภอเมืองนครราชสีมา จังหวัดนครราชสีมา ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง จำนวน 1 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=185a0dfc-62ed-4497-966a-c01f547f4cfe</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b01336ca-7547-423f-beb5-e3a81696e22b</t>
         </is>
       </c>
     </row>
@@ -2713,15 +2713,15 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>สำนักงานประกันสังคม</t>
+          <t>สำนักงานพัฒนาวิทยาศาสตร์และเทคโนโลยีแห่งชาติ</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1706</v>
+        <v>1905</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง จำนวน 1 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อระบบครุภัณฑ์สนับสนุนการพัฒนาเศรษฐกิจชีวภาพ เศรษฐกิจหมุนเวียน และเศรษฐกิจสีเขียว ตำบลคลองหนึ่ง อำเภอคลองหลวง จังหวัดปทุมธานี 1 ระบบ เครื่องปั่นเหวี่ยงความเร็วสูง (Superspeed centrifuge) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2736,27 +2736,27 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b01336ca-7547-423f-beb5-e3a81696e22b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=359b6f0b-0eeb-4b7f-9d76-b98fb3fa120d</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>สำนักงานพัฒนาวิทยาศาสตร์และเทคโนโลยีแห่งชาติ</t>
+          <t>ศูนย์อำนวยการรักษาผลประโยชน์ของชาติทางทะเล</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1905</v>
+        <v>138</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อระบบครุภัณฑ์สนับสนุนการพัฒนาเศรษฐกิจชีวภาพ เศรษฐกิจหมุนเวียน และเศรษฐกิจสีเขียว ตำบลคลองหนึ่ง อำเภอคลองหลวง จังหวัดปทุมธานี 1 ระบบ เครื่องปั่นเหวี่ยงความเร็วสูง (Superspeed centrifuge) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องคอมพิวเตอร์โน้ตบุ๊ก สำหรับงานประมวลผล จำนวน ๒๒ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2766,12 +2766,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, โน้ตบุ๊ก)</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=359b6f0b-0eeb-4b7f-9d76-b98fb3fa120d</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=809976d2-f842-4f28-993b-5dbf2627d012</t>
         </is>
       </c>
     </row>
@@ -2783,17 +2783,15 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ศูนย์อำนวยการรักษาผลประโยชน์ของชาติทางทะเล</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>0138</t>
-        </is>
+          <t>สำนักงานปลัดกระทรวงกลาโหม</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>201</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องคอมพิวเตอร์โน้ตบุ๊ก สำหรับงานประมวลผล จำนวน ๒๒ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์แผนกแผนและโครงการ รบท.อท.ศอพท. จำนวน 5 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2803,12 +2801,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, โน้ตบุ๊ก)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=809976d2-f842-4f28-993b-5dbf2627d012</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=24573f9d-aa0a-45b1-91fc-930f70268f4e</t>
         </is>
       </c>
     </row>
@@ -2820,17 +2818,15 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงกลาโหม</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>0201</t>
-        </is>
+          <t>กรมสรรพากร</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>307</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์แผนกแผนและโครงการ รบท.อท.ศอพท. จำนวน 5 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อวัสดุสิ้นเปลืองเพื่อใช้กับระบบเครื่องพิมพ์ต่อเนื่องความเร็วสูง เพื่อใช้สำหรับพิมพ์เอกสารทางภาษี ประจำปี พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2840,12 +2836,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (เครื่องพิมพ์)</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=24573f9d-aa0a-45b1-91fc-930f70268f4e</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c848bed5-5bad-40b5-8056-82b6f95bfae2</t>
         </is>
       </c>
     </row>
@@ -2857,17 +2853,15 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>กรมสรรพากร</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>0307</t>
-        </is>
+          <t>กรมการข้าว</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>718</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการจัดซื้อวัสดุสิ้นเปลืองเพื่อใช้กับระบบเครื่องพิมพ์ต่อเนื่องความเร็วสูง เพื่อใช้สำหรับพิมพ์เอกสารทางภาษี ประจำปี พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การเกษตร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2877,12 +2871,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>★ (เครื่องพิมพ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c848bed5-5bad-40b5-8056-82b6f95bfae2</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8218601d-a676-42ae-849d-028704cbe916</t>
         </is>
       </c>
     </row>
@@ -2894,17 +2888,15 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>กรมการข้าว</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>0718</t>
-        </is>
+          <t>กรมท่าอากาศยาน</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>805</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การเกษตร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างงานจ้างเหมาทำความสะอาดอาคารที่พักผู้โดยสาร และเก็บรถเข็นสัมภาระผู้โดยสารที่ท่าอากาศยานลำปาง ประจำปีงบประมาณ ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2914,12 +2906,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (รถเข็น)</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8218601d-a676-42ae-849d-028704cbe916</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=182d87d4-9f00-4361-9f26-bcf65839d3d5</t>
         </is>
       </c>
     </row>
@@ -2931,17 +2923,15 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>กรมท่าอากาศยาน</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>0805</t>
-        </is>
+          <t>กรมโยธาธิการและผังเมือง</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>1507</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างงานจ้างเหมาทำความสะอาดอาคารที่พักผู้โดยสาร และเก็บรถเข็นสัมภาระผู้โดยสารที่ท่าอากาศยานลำปาง ประจำปีงบประมาณ ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างก่อสร้างโครงการก่อสร้างเขื่อนป้องกันตลิ่งริมแม่น้ำยม บ้านวังต้นเกลือ หมู่ที่ 7 ตำบลปากกาง อำเภอลอง จังหวัดแพร่ ความยาวไม่น้อยกว่า 1,000 เมตร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2951,34 +2941,34 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>★ (รถเข็น)</t>
+          <t>★ (ปากกา)</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=182d87d4-9f00-4361-9f26-bcf65839d3d5</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2815a715-ddfc-40d8-b3e8-78d6367955f5</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>กรมโยธาธิการและผังเมือง</t>
+          <t>สำนักงานเศรษฐกิจการคลัง</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>1507</t>
+          <t>0311</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างก่อสร้างโครงการก่อสร้างเขื่อนป้องกันตลิ่งริมแม่น้ำยม บ้านวังต้นเกลือ หมู่ที่ 7 ตำบลปากกาง อำเภอลอง จังหวัดแพร่ ความยาวไม่น้อยกว่า 1,000 เมตร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการต่ออายุ License ของซอฟต์แวร์ตรวจจับและตอบสนอง ต่อภัยคุกคามทางไซเบอร์ (Endpoint Detection and Response  EDR) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2988,12 +2978,271 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>★ (ปากกา)</t>
+          <t>★ (ซอฟต์แวร์)</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2815a715-ddfc-40d8-b3e8-78d6367955f5</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=94729b88-7aec-43e6-9dcb-0fd5f83cf536</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>กรมส่งเสริมและพัฒนาคุณภาพชีวิตคนพิการ</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>0607</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์งานบ้านงานครัวและครุภัณฑ์สำนักงาน จำนวน ๒๕ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=68659363-920b-4d6a-80fa-3d50e542f641</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>กรมการข้าว</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>0718</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c5b19896-e529-4c05-a497-b6f318a91a77</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>กรมท่าอากาศยาน</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างเหมาทำความสะอาดที่พักผู้โดยสาร รวมทั้งอาคารต่าง ๆ และเก็บรถเข็นสัมภาระผู้โดยสาร ที่ท่าอากาศยานสุราษฎร์ธานี ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>★ (รถเข็น)</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=772b1ba1-dc6a-4f2c-ad6a-7b9398a81899</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>กรมทางหลวง</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>0806</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างงานจ้างเหมาบริหารจัดการระบบควบคุมการอำนวยการจราจรด้านความปลอดภัยศูนย์บริหารจัดการจราจรกลางมอเตอร์เวย์ (Traffic Management Center) ลาดกระบังและพัทยา พร้อมปรับปรุงโปรแกรมระบบเพื่อรองรับความต้องการของผู้ใช้งานเพิ่มเติม ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>★ (มอเตอร์)</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a5144693-ef25-4928-be3e-49b03193e74c</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>กรมที่ดิน</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>1505</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อวัสดุหมึกพิมพ์ จำนวน ๓๖ รายการ สำหรับใช้ในราชการกองเทคโนโลยีทำแผนที่ ประจำปีงบประมาณ พ.ศ. ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>★ (หมึกพิมพ์)</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=aabc5e98-123d-4aca-81d1-decdb50fe286</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>สำนักงานพัฒนาเทคโนโลยีอวกาศและภูมิสารสนเทศ (องค์การมหาชน)</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>1906</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์คอมพิวเตอร์และอุปกรณ์ต่อพ่วงสำหรับการบริการข้อมูลดาวเทียม ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a78cc797-5c4c-405a-8950-d7cf8b14e796</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง รายการรถพยาบาลพร้อมอุปกรณ์ช่วยชีวิตขั้นสูง จำนวน 2 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=141cb2cf-43e6-4593-806a-e73fbfa47ecf</t>
         </is>
       </c>
     </row>

--- a/Backup/eGP_Monthly_Main_202608.xlsx
+++ b/Backup/eGP_Monthly_Main_202608.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1243,15 +1243,15 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>กรมการข้าว</t>
+          <t>กรมทางหลวง</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>718</v>
+        <v>806</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์สำนักงาน จำนวน 2 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1261,12 +1261,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=89d58d6c-21eb-4b00-ae18-73e2e8debfcd</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=16595160-097a-47eb-ad52-50c6ac0669b6</t>
         </is>
       </c>
     </row>
@@ -1278,15 +1278,15 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>กรมทางหลวง</t>
+          <t>องค์การกระจายเสียงและแพร่ภาพสาธารณะแห่งประเทศไทย(ส.ส.ท.)</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>806</v>
+        <v>915</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์สำนักงาน จำนวน 2 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบริหารโครงการปรับปรุง-ซ่อมแซม เสาส่งสัญญาณโทรทัศน์ จำนวน 3 ต้น (ครั้งที่ 2) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1296,12 +1296,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
+          <t>★ (โทรทัศน์)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=16595160-097a-47eb-ad52-50c6ac0669b6</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d3f92b84-8942-4a5e-8b71-09a3b50f22b8</t>
         </is>
       </c>
     </row>
@@ -1313,15 +1313,15 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>องค์การกระจายเสียงและแพร่ภาพสาธารณะแห่งประเทศไทย(ส.ส.ท.)</t>
+          <t>กรมการปกครอง</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>915</v>
+        <v>1503</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบริหารโครงการปรับปรุง-ซ่อมแซม เสาส่งสัญญาณโทรทัศน์ จำนวน 3 ต้น (ครั้งที่ 2) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อวัสดุสำหรับเครื่องพิมพ์คอมพิวเตอร์ ประจำปีงบประมาณ พ.ศ. 2569 จำนวน 6 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1331,12 +1331,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>★ (โทรทัศน์)</t>
+          <t>★ (คอมพิวเตอร์, เครื่องพิมพ์)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d3f92b84-8942-4a5e-8b71-09a3b50f22b8</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=cbd87cdd-c675-49aa-86c1-06701a31d08c</t>
         </is>
       </c>
     </row>
@@ -1348,15 +1348,15 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>กรมการปกครอง</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1503</v>
+        <v>2102</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อวัสดุสำหรับเครื่องพิมพ์คอมพิวเตอร์ ประจำปีงบประมาณ พ.ศ. 2569 จำนวน 6 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง  รายการรถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิิ้ลแค็บ จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1366,12 +1366,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, เครื่องพิมพ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=cbd87cdd-c675-49aa-86c1-06701a31d08c</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3542ee80-4348-403e-9bc6-77eb374130af</t>
         </is>
       </c>
     </row>
@@ -1383,15 +1383,15 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กรมควบคุมโรค</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2102</v>
+        <v>2104</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง  รายการรถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิิ้ลแค็บ จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องคอมพิวเตอร์โน้ตบุ๊ก สำหรับงานประมวลผล จำนวน 35 เครื่อง โดยวิธีประกาศเชิญชวนทั่วไป ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1401,12 +1401,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, โน้ตบุ๊ก)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3542ee80-4348-403e-9bc6-77eb374130af</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8ef67de6-f58f-45c6-8c3c-a301a465905f</t>
         </is>
       </c>
     </row>
@@ -1418,15 +1418,15 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>กรมควบคุมโรค</t>
+          <t>กรมวิทยาศาสตร์การแพทย์</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2104</v>
+        <v>2106</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องคอมพิวเตอร์โน้ตบุ๊ก สำหรับงานประมวลผล จำนวน 35 เครื่อง โดยวิธีประกาศเชิญชวนทั่วไป ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อน้ำยาสำหรับตรวจคัดกรองทารกแรกเกิดในกลุ่มโรคพันธุกรรมเมตาบอลิก (Inherited Metabolic DisordersIEM) จากกระดาษซับเลือด จำนวน ๓๕ กล่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1436,12 +1436,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, โน้ตบุ๊ก)</t>
+          <t>★ (กระดาษ)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8ef67de6-f58f-45c6-8c3c-a301a465905f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9d8080df-2cf1-44d2-8bea-f0761f4fcf27</t>
         </is>
       </c>
     </row>
@@ -1453,15 +1453,15 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>กรมวิทยาศาสตร์การแพทย์</t>
+          <t>สถาบันพระบรมราชชนก</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2106</v>
+        <v>2117</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อน้ำยาสำหรับตรวจคัดกรองทารกแรกเกิดในกลุ่มโรคพันธุกรรมเมตาบอลิก (Inherited Metabolic DisordersIEM) จากกระดาษซับเลือด จำนวน ๓๕ กล่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อประกวดราคาซื้อครุภัณฑ์โฆษณาและเผยแพร่ จำนวน 21 รายการ ประจำปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1471,12 +1471,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>★ (กระดาษ)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9d8080df-2cf1-44d2-8bea-f0761f4fcf27</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=11c8851e-8e7e-49c2-85f2-94cc884f2e73</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อประกวดราคาซื้อครุภัณฑ์โฆษณาและเผยแพร่ จำนวน 21 รายการ ประจำปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์คอมพิวเตอร์ขนาดเล็กที่มีมูลค่าไม่เกิน ๕ ล้านบาท ประจำปีงบประมาณ พ.ศ. ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1506,12 +1506,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=11c8851e-8e7e-49c2-85f2-94cc884f2e73</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c233d882-7c26-4c1d-9eef-c0205512d68d</t>
         </is>
       </c>
     </row>
@@ -1523,15 +1523,15 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>สถาบันพระบรมราชชนก</t>
+          <t>สำนักงานคณะกรรมการพิเศษเพื่อประสานงานโครงการอันเนื่องมาจากพระราชดำริ</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2117</v>
+        <v>2504</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์คอมพิวเตอร์ขนาดเล็กที่มีมูลค่าไม่เกิน ๕ ล้านบาท ประจำปีงบประมาณ พ.ศ. ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาติดตั้งกล้องโทรทัศน์วงจรปิดสำหรับใช้ในงานรักษา ความปลอดภัยทั่วไปและงานอื่น ๆ บริเวณอาคารโครงการอันเนื่องมาจากพระราชดำริ ประจำปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1541,32 +1541,32 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (โทรทัศน์)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c233d882-7c26-4c1d-9eef-c0205512d68d</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6ce2f91f-a687-49d1-bebb-fc4647123ff8</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>สำนักงานคณะกรรมการพิเศษเพื่อประสานงานโครงการอันเนื่องมาจากพระราชดำริ</t>
+          <t>สำนักงานกองทุนสนับสนุนการสร้างเสริมสุขภาพ</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2504</v>
+        <v>117</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาติดตั้งกล้องโทรทัศน์วงจรปิดสำหรับใช้ในงานรักษา ความปลอดภัยทั่วไปและงานอื่น ๆ บริเวณอาคารโครงการอันเนื่องมาจากพระราชดำริ ประจำปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อระบบป้องกันและตรวจจับภัยคุกคามบนเครื่องคอมพิวเตอร์ (Endpoint Detection and Response EDR) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>★ (โทรทัศน์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6ce2f91f-a687-49d1-bebb-fc4647123ff8</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1c672e2a-4730-48d3-bcc5-6ffdfd7ae5e6</t>
         </is>
       </c>
     </row>
@@ -1593,15 +1593,15 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>สำนักงานกองทุนสนับสนุนการสร้างเสริมสุขภาพ</t>
+          <t>กรมสรรพสามิต</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>117</v>
+        <v>306</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อระบบป้องกันและตรวจจับภัยคุกคามบนเครื่องคอมพิวเตอร์ (Endpoint Detection and Response EDR) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการซื้อผงหมึกสำหรับใช้กับเครื่องพิมพ์คอมพิวเตอร์แบบเลเซอร์ ชนิดสี จำนวน ๔ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (คอมพิวเตอร์, เครื่องพิมพ์)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1c672e2a-4730-48d3-bcc5-6ffdfd7ae5e6</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e98eb1c6-980c-4595-871a-1897574b2734</t>
         </is>
       </c>
     </row>
@@ -1628,15 +1628,15 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>กรมสรรพสามิต</t>
+          <t>กรมวิชาการเกษตร</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>306</v>
+        <v>709</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการซื้อผงหมึกสำหรับใช้กับเครื่องพิมพ์คอมพิวเตอร์แบบเลเซอร์ ชนิดสี จำนวน ๔ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาเคลื่อนย้ายและติดตั้งครุภัณฑ์  จำนวน 58 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1646,12 +1646,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, เครื่องพิมพ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e98eb1c6-980c-4595-871a-1897574b2734</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4bdd5427-3392-4059-816e-a14011b5c2c2</t>
         </is>
       </c>
     </row>
@@ -1663,15 +1663,15 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>กรมวิชาการเกษตร</t>
+          <t>กรมที่ดิน</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>709</v>
+        <v>1505</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาเคลื่อนย้ายและติดตั้งครุภัณฑ์  จำนวน 58 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์พร้อมอุปกรณ์ จำนวน ๑๑ รายการ สำหรับใช้ในราชการหน่วยงานต่าง ๆ รวม ๓ แห่ง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1681,12 +1681,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4bdd5427-3392-4059-816e-a14011b5c2c2</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=78f7da52-221c-49ba-aabe-eb85e9677acd</t>
         </is>
       </c>
     </row>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์พร้อมอุปกรณ์ จำนวน ๑๑ รายการ สำหรับใช้ในราชการหน่วยงานต่าง ๆ รวม ๓ แห่ง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างพิมพ์แบบพิมพ์ใบเสร็จรับเงินค่าธรรมเนียมฯ ชนิดใช้กับเครื่องคอมพิวเตอร์ จำนวน ๑๒,๐๐๐,๐๐๐ ชุด (๑๒,๐๐๐ กล่อง) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1716,12 +1716,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=78f7da52-221c-49ba-aabe-eb85e9677acd</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6e2f2cd5-d34f-496a-b061-5311fba83a12</t>
         </is>
       </c>
     </row>
@@ -1733,15 +1733,15 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>กรมที่ดิน</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1505</v>
+        <v>2102</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างพิมพ์แบบพิมพ์ใบเสร็จรับเงินค่าธรรมเนียมฯ ชนิดใช้กับเครื่องคอมพิวเตอร์ จำนวน ๑๒,๐๐๐,๐๐๐ ชุด (๑๒,๐๐๐ กล่อง) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ทันตกรรม จำนวน ๖ รายการ รพ.สต.บางพูด ปีงบประมาณ ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1751,12 +1751,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6e2f2cd5-d34f-496a-b061-5311fba83a12</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4537f82a-c1fd-4f34-b3aa-edbfc090fe7f</t>
         </is>
       </c>
     </row>
@@ -1776,7 +1776,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ทันตกรรม จำนวน ๖ รายการ รพ.สต.บางพูด ปีงบประมาณ ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อรถยนต์ไฟฟ้าประเภทผสมหรือไฮบริด (HEV)ปริมาตรกระบอกสูบไม่เกิน 2,000 ซีซี หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 60 กิโลวัตต์ และกำลังมอเตอร์ไฟฟ้าสูงสุดไม่เกิน 115 กิโลวัตต์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (มอเตอร์)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4537f82a-c1fd-4f34-b3aa-edbfc090fe7f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=636c511e-19c5-419f-857a-d7a3b2ee7266</t>
         </is>
       </c>
     </row>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อรถยนต์ไฟฟ้าประเภทผสมหรือไฮบริด (HEV)ปริมาตรกระบอกสูบไม่เกิน 2,000 ซีซี หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 60 กิโลวัตต์ และกำลังมอเตอร์ไฟฟ้าสูงสุดไม่เกิน 115 กิโลวัตต์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาเช่าเครื่องคอมพิวเตอร์สำหรับงานสำนักงานและเครื่องคอมพิวเตอร์สำหรับงานประมวลผล จำนวน ๒ รายการ ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1821,32 +1821,32 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>★ (มอเตอร์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=636c511e-19c5-419f-857a-d7a3b2ee7266</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=bfa365d5-c79f-471b-9719-ebef768e86ed</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กรมพัฒนาที่ดิน</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2102</v>
+        <v>708</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ประกวดราคาเช่าเครื่องคอมพิวเตอร์สำหรับงานสำนักงานและเครื่องคอมพิวเตอร์สำหรับงานประมวลผล จำนวน ๒ รายการ ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถกอล์ฟไฟฟ้า ขนาด ๒๓ ที่นั่ง จำนวน ๑ คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1856,12 +1856,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=bfa365d5-c79f-471b-9719-ebef768e86ed</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ec98788a-c085-48e5-9170-fc39dcb3b80e</t>
         </is>
       </c>
     </row>
@@ -1873,15 +1873,15 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>กรมพัฒนาที่ดิน</t>
+          <t>กรมท่าอากาศยาน</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>708</v>
+        <v>805</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถกอล์ฟไฟฟ้า ขนาด ๒๓ ที่นั่ง จำนวน ๑ คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างงานจ้างเหมาทำความสะอาดอาคารที่พักผู้โดยสาร รวมทั้งอาคารทำการต่างๆ และเก็บรถเข็นสัมภาระผู้โดยสาร ที่ท่าอากาศยานนครศรีธรรมราช ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1891,12 +1891,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (รถเข็น)</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ec98788a-c085-48e5-9170-fc39dcb3b80e</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=df9a63c8-8a11-4af7-90ff-7075e75f6f70</t>
         </is>
       </c>
     </row>
@@ -1908,15 +1908,15 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>กรมท่าอากาศยาน</t>
+          <t>กรมการปกครอง</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>805</v>
+        <v>1503</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างงานจ้างเหมาทำความสะอาดอาคารที่พักผู้โดยสาร รวมทั้งอาคารทำการต่างๆ และเก็บรถเข็นสัมภาระผู้โดยสาร ที่ท่าอากาศยานนครศรีธรรมราช ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาเช่าระบบคอมพิวเตอร์และอุปกรณ์ประกอบตามโครงการจัดหาระบบคอมพิวเตอร์เพื่อให้บริการประชาชนทางด้านทะเบียนและบัตรประจำตัวประชาชน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1926,12 +1926,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>★ (รถเข็น)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=df9a63c8-8a11-4af7-90ff-7075e75f6f70</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=aaa01898-82c5-4979-98ad-3b924e56fa5e</t>
         </is>
       </c>
     </row>
@@ -1943,15 +1943,15 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>กรมการปกครอง</t>
+          <t>กรมสนับสนุนบริการสุขภาพ</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1503</v>
+        <v>2107</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ประกวดราคาเช่าระบบคอมพิวเตอร์และอุปกรณ์ประกอบตามโครงการจัดหาระบบคอมพิวเตอร์เพื่อให้บริการประชาชนทางด้านทะเบียนและบัตรประจำตัวประชาชน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุกไฟฟ้า ประเภทแบตเตอรี่ (BEV) จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1961,32 +1961,32 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=aaa01898-82c5-4979-98ad-3b924e56fa5e</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7942968c-7119-4de3-89a6-67f0c3219a77</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>กรมสนับสนุนบริการสุขภาพ</t>
+          <t>ศูนย์อำนวยการรักษาผลประโยชน์ของชาติทางทะเล</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2107</v>
+        <v>138</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุกไฟฟ้า ประเภทแบตเตอรี่ (BEV) จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องคอมพิวเตอร์ สำนักงาน จำนวน ๖๑ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7942968c-7119-4de3-89a6-67f0c3219a77</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c5565b35-992b-42db-9382-5cd4d0a93a45</t>
         </is>
       </c>
     </row>
@@ -2013,15 +2013,15 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ศูนย์อำนวยการรักษาผลประโยชน์ของชาติทางทะเล</t>
+          <t>สำนักงานพิพิธภัณฑ์เกษตรเฉลิมพระเกียรติพระบาทสมเด็จพระเจ้าอยู่หัว (องค์การมหาชน)</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>138</v>
+        <v>719</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องคอมพิวเตอร์ สำนักงาน จำนวน ๖๑ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อระบบเครื่องปรับอากาศแบบชิลเลอร์ พร้อมติดตั้ง ตำบลคลองหนึ่ง อำเภอคลองหลวง จังหวัดปทุมธานี 1 งาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (เครื่องปรับอากาศ)</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c5565b35-992b-42db-9382-5cd4d0a93a45</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f199228b-fa95-4f46-bc8d-7d292acae98f</t>
         </is>
       </c>
     </row>
@@ -2048,15 +2048,15 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>สำนักงานพิพิธภัณฑ์เกษตรเฉลิมพระเกียรติพระบาทสมเด็จพระเจ้าอยู่หัว (องค์การมหาชน)</t>
+          <t>กรมท่าอากาศยาน</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>719</v>
+        <v>805</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อระบบเครื่องปรับอากาศแบบชิลเลอร์ พร้อมติดตั้ง ตำบลคลองหนึ่ง อำเภอคลองหลวง จังหวัดปทุมธานี 1 งาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาทำความสะอาดอาคารที่พักผู้โดยสาร รวมทั้งอาคารทำการต่าง ๆ และเก็บรถเข็นสัมภาระผู้โดยสาร ที่ท่าอากาศยานน่านนคร ประจำปีงบประมาณ 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>★ (เครื่องปรับอากาศ)</t>
+          <t>★ (รถเข็น)</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f199228b-fa95-4f46-bc8d-7d292acae98f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=651d40b6-b435-41c6-8873-70362ee1f386</t>
         </is>
       </c>
     </row>
@@ -2083,15 +2083,15 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>กรมท่าอากาศยาน</t>
+          <t>กรมทางหลวง</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาทำความสะอาดอาคารที่พักผู้โดยสาร รวมทั้งอาคารทำการต่าง ๆ และเก็บรถเข็นสัมภาระผู้โดยสาร ที่ท่าอากาศยานน่านนคร ประจำปีงบประมาณ 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 8 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>★ (รถเข็น)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=651d40b6-b435-41c6-8873-70362ee1f386</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1b7a05b0-a0f5-4072-9eba-b67d1bbfac34</t>
         </is>
       </c>
     </row>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 8 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างก่อสร้างงานป้ายจราจร (Road Sign) ชนิดป้ายเตือนความเร็วระบบตรวจวัดอัตโนมัติ (Your Speed Sign) ตามแบบแขวงทางหลวงพิเศษระหว่างเมือง ทางหลวงพิเศษหมายเลข ๙ ตอน บางปะอิน - บางพลี ที่ กม.๗+๒๐๐ - กม.๓๖+๒๐๐ LT., RT. (เป็นช่วง ๆ) ปริมาณงาน ๑๘.๐๐ ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (ป้ายเตือน)</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1b7a05b0-a0f5-4072-9eba-b67d1bbfac34</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ef72a1b7-8bcd-48ac-b53d-2c18897908fc</t>
         </is>
       </c>
     </row>
@@ -2161,7 +2161,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างก่อสร้างงานป้ายจราจร (Road Sign) ชนิดป้ายเตือนความเร็วระบบตรวจวัดอัตโนมัติ (Your Speed Sign) ตามแบบแขวงทางหลวงพิเศษระหว่างเมือง ทางหลวงพิเศษหมายเลข ๙ ตอน บางปะอิน - บางพลี ที่ กม.๗+๒๐๐ - กม.๓๖+๒๐๐ LT., RT. (เป็นช่วง ๆ) ปริมาณงาน ๑๘.๐๐ ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างก่อสร้างงานป้ายจราจร (Road Sign) ชนิดป้ายเตือนความเร็วระบบตรวจวัดอัตโนมัติ (Your Speed Sign) ตามแบบแขวงทางหลวงพิเศษระหว่างเมือง ทางหลวงพิเศษหมายเลข ๗ ตอน หนองข้างคอก - ตะเคียนเตี้ย กม.๗๘+๑๐๐ - กม.๙๔+๕๐๐ LT., RT. (เป็นช่วง ๆ) ปริมาณงาน ๑๘.๐๐ ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ef72a1b7-8bcd-48ac-b53d-2c18897908fc</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6c76342a-837c-438f-afb8-73a77b63f5d1</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างก่อสร้างงานป้ายจราจร (Road Sign) ชนิดป้ายเตือนความเร็วระบบตรวจวัดอัตโนมัติ (Your Speed Sign) ตามแบบแขวงทางหลวงพิเศษระหว่างเมือง ทางหลวงพิเศษหมายเลข ๗ ตอน หนองข้างคอก - ตะเคียนเตี้ย กม.๗๘+๑๐๐ - กม.๙๔+๕๐๐ LT., RT. (เป็นช่วง ๆ) ปริมาณงาน ๑๘.๐๐ ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างก่อสร้างงานป้ายจราจร (Road Sign) ชนิดป้ายเตือนความเร็วระบบตรวจวัดอัตโนมัติ (Your Speed Sign) ตามแบบแขวงทางหลวงพิเศษระหว่างเมือง ทางหลวงพิเศษหมายเลข ๗ ตอน แขวงคลองสองต้นนุ่น - ตะเคียนเตี้ย กม.๑๙+๙๑๐ - กม.๗๘+๑๐๐ LT., RT. (เป็นช่วง ๆ) ปริมาณงาน ๑๗.๐๐ ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6c76342a-837c-438f-afb8-73a77b63f5d1</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8e26d004-4627-4bfe-b31a-5fbfb958c14d</t>
         </is>
       </c>
     </row>
@@ -2223,15 +2223,15 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>กรมทางหลวง</t>
+          <t>กรมการจัดหางาน</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>806</v>
+        <v>1703</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างก่อสร้างงานป้ายจราจร (Road Sign) ชนิดป้ายเตือนความเร็วระบบตรวจวัดอัตโนมัติ (Your Speed Sign) ตามแบบแขวงทางหลวงพิเศษระหว่างเมือง ทางหลวงพิเศษหมายเลข ๗ ตอน แขวงคลองสองต้นนุ่น - ตะเคียนเตี้ย กม.๑๙+๙๑๐ - กม.๗๘+๑๐๐ LT., RT. (เป็นช่วง ๆ) ปริมาณงาน ๑๗.๐๐ ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์โครงการจัดหาครุภัณฑ์คอมพิวเตอร์สำหรับศูนย์ร่วมบริการช่วยเหลือแรงงานต่างด้าวประจำปีงบประมาณ พ.ศ. ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2241,12 +2241,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>★ (ป้ายเตือน)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8e26d004-4627-4bfe-b31a-5fbfb958c14d</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d4861cb6-80c0-4cc3-9e19-243722109b1c</t>
         </is>
       </c>
     </row>
@@ -2258,15 +2258,15 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>กรมการจัดหางาน</t>
+          <t>กรมส่งเสริมการเรียนรู้</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1703</v>
+        <v>2033</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์โครงการจัดหาครุภัณฑ์คอมพิวเตอร์สำหรับศูนย์ร่วมบริการช่วยเหลือแรงงานต่างด้าวประจำปีงบประมาณ พ.ศ. ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างโครงการการประชาสัมพันธ์การประกวดออกแบบ ห้องสมุดแห่งการอ่าน พลิกโฉมศูนย์การเรียนรู้ตลอดชีวิตประจำจังหวัด (เฟสที่ ๑) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2276,12 +2276,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (สมุด)</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d4861cb6-80c0-4cc3-9e19-243722109b1c</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a1502f63-3bc7-4991-8c91-3aae4697691f</t>
         </is>
       </c>
     </row>
@@ -2293,15 +2293,15 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>กรมส่งเสริมการเรียนรู้</t>
+          <t>สถาบันพระบรมราชชนก</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>2033</v>
+        <v>2117</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างโครงการการประชาสัมพันธ์การประกวดออกแบบ ห้องสมุดแห่งการอ่าน พลิกโฉมศูนย์การเรียนรู้ตลอดชีวิตประจำจังหวัด (เฟสที่ ๑) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์สำนักงาน ๙ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2311,32 +2311,32 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>★ (สมุด)</t>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a1502f63-3bc7-4991-8c91-3aae4697691f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=62dec7df-5ef3-440a-8894-cdac556ab7e6</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>สถาบันพระบรมราชชนก</t>
+          <t>กองทัพบก</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>2117</v>
+        <v>204</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์สำนักงาน ๙ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อชิ้นส่วนซ่อมคอมพิวเตอร์และอุปกรณ์ประกอบ เเละชิ้นส่วนซ่อมคอมพิวเตอร์ซ่อมเคลื่อนที่ (สนับสนุน บชร.1-4) จำนวน 21 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2346,12 +2346,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=62dec7df-5ef3-440a-8894-cdac556ab7e6</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9288bd0f-8fd4-4029-900a-3e27850eac64</t>
         </is>
       </c>
     </row>
@@ -2363,15 +2363,15 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>กองทัพบก</t>
+          <t>กองทัพอากาศ</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อชิ้นส่วนซ่อมคอมพิวเตอร์และอุปกรณ์ประกอบ เเละชิ้นส่วนซ่อมคอมพิวเตอร์ซ่อมเคลื่อนที่ (สนับสนุน บชร.1-4) จำนวน 21 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องคอมพิวเตอร์โน้ตบุ๊ก สำหรับงานประมวลผล พร้อมติดตั้ง โปรแกรมระบบปฏิบัติการที่มีลิขสิทธิ์ถูกต้องตามกฎหมาย  จำนวน 14 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2381,12 +2381,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (คอมพิวเตอร์, โน้ตบุ๊ก, ระบบปฏิบัติการ)</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9288bd0f-8fd4-4029-900a-3e27850eac64</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c3261ee7-89c8-4302-a803-5214f9dd5652</t>
         </is>
       </c>
     </row>
@@ -2398,15 +2398,15 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>กองทัพอากาศ</t>
+          <t>กองบัญชาการกองทัพไทย</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องคอมพิวเตอร์โน้ตบุ๊ก สำหรับงานประมวลผล พร้อมติดตั้ง โปรแกรมระบบปฏิบัติการที่มีลิขสิทธิ์ถูกต้องตามกฎหมาย  จำนวน 14 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อชิ้นส่วนซ่อมบำรุง, เครื่องมือสำรองทดแทน, เครื่องมือซ่อมบำรุงและสิ่งอำนวยความสะดวกระบบคอมพิวเตอร์และเครือข่าย ตามโครงการส่งกำลังและซ่อมบำรุง กรมการสื่อสารทหาร กองบัญชาการกองทัพไทย  ระยะที่ 2 ประจำปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2416,12 +2416,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, โน้ตบุ๊ก, ระบบปฏิบัติการ)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c3261ee7-89c8-4302-a803-5214f9dd5652</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d02761df-5af1-4901-b0e4-55d84955ca87</t>
         </is>
       </c>
     </row>
@@ -2433,15 +2433,15 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>กองบัญชาการกองทัพไทย</t>
+          <t>กรมบัญชีกลาง</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>208</v>
+        <v>304</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อชิ้นส่วนซ่อมบำรุง, เครื่องมือสำรองทดแทน, เครื่องมือซ่อมบำรุงและสิ่งอำนวยความสะดวกระบบคอมพิวเตอร์และเครือข่าย ตามโครงการส่งกำลังและซ่อมบำรุง กรมการสื่อสารทหาร กองบัญชาการกองทัพไทย  ระยะที่ 2 ประจำปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อการจัดซื้อผงหมึกเครื่องพิมพ์ จำนวน 6 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (หมึกเครื่องพิมพ์, เครื่องพิมพ์)</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d02761df-5af1-4901-b0e4-55d84955ca87</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a765d638-98e1-4dd8-a368-7357c6452f7d</t>
         </is>
       </c>
     </row>
@@ -2468,15 +2468,15 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>กรมบัญชีกลาง</t>
+          <t>กรมท่าอากาศยาน</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>304</v>
+        <v>805</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อการจัดซื้อผงหมึกเครื่องพิมพ์ จำนวน 6 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างจ้างเหมาทำความสะอาดอาคารที่พักผู้โดยสาร รวมทั้งอาคารทำการต่างๆ และเก็บรถเข็นสัมภาระผู้โดยสาร ที่ท่าอากาศยานอุบลราชธานี ประจำปีงบประมาณ 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>★ (หมึกเครื่องพิมพ์, เครื่องพิมพ์)</t>
+          <t>★ (รถเข็น)</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a765d638-98e1-4dd8-a368-7357c6452f7d</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7ce2815f-417a-40f8-98f0-f3ad5fcfb5f4</t>
         </is>
       </c>
     </row>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างจ้างเหมาทำความสะอาดอาคารที่พักผู้โดยสาร รวมทั้งอาคารทำการต่างๆ และเก็บรถเข็นสัมภาระผู้โดยสาร ที่ท่าอากาศยานอุบลราชธานี ประจำปีงบประมาณ 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาทำความสะอาดอาคารที่พักผู้โดยสาร รวมทั้งอาคารทำการต่างๆ และเก็บรถเข็นสัมภาระผู้โดยสาร ที่ท่าอากาศยานระนอง ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7ce2815f-417a-40f8-98f0-f3ad5fcfb5f4</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e270c130-86b2-4ca1-b931-b0cdd527deae</t>
         </is>
       </c>
     </row>
@@ -2546,7 +2546,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาทำความสะอาดอาคารที่พักผู้โดยสาร รวมทั้งอาคารทำการต่างๆ และเก็บรถเข็นสัมภาระผู้โดยสาร ที่ท่าอากาศยานระนอง ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาทำความสะอาดอาคารที่พักผู้โดยสาร รวมทั้งอาคารทำการต่างๆ และเก็บรถเข็นสัมภาระผู้โดยสาร ที่ท่าอากาศยานอุดรธานี ประจำปีงบประมาณ ๒๕๗๐ ระยะเวลาจ้าง ๑๒ เดือน ตั้งแต่วันที่ ๑ ตุลาคม ๒๕๖๙ ถึงวันที่ ๓๐ กันยายน ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e270c130-86b2-4ca1-b931-b0cdd527deae</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c68bceb0-a225-44d1-9f01-2755bf635f6d</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาทำความสะอาดอาคารที่พักผู้โดยสาร รวมทั้งอาคารทำการต่างๆ และเก็บรถเข็นสัมภาระผู้โดยสาร ที่ท่าอากาศยานอุดรธานี ประจำปีงบประมาณ ๒๕๗๐ ระยะเวลาจ้าง ๑๒ เดือน ตั้งแต่วันที่ ๑ ตุลาคม ๒๕๖๙ ถึงวันที่ ๓๐ กันยายน ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างงานจ้างเหมาทำความสะอาดอาคารที่พักผู้โดยสาร รวมทั้งอาคารทำการต่าง ๆ และเก็บรถเข็นสัมภาระผู้โดยสาร ที่ท่าอากาศยานสกลนคร ประจำปีงบประมาณ 2570 (เดือน ตุลาคม 2569 - เดือน กันยายน 2570) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c68bceb0-a225-44d1-9f01-2755bf635f6d</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=63c26320-0a57-49c2-b838-a56d90ad3d33</t>
         </is>
       </c>
     </row>
@@ -2608,15 +2608,15 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>กรมท่าอากาศยาน</t>
+          <t>กรมการปกครอง</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>805</v>
+        <v>1503</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างงานจ้างเหมาทำความสะอาดอาคารที่พักผู้โดยสาร รวมทั้งอาคารทำการต่าง ๆ และเก็บรถเข็นสัมภาระผู้โดยสาร ที่ท่าอากาศยานสกลนคร ประจำปีงบประมาณ 2570 (เดือน ตุลาคม 2569 - เดือน กันยายน 2570) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ประกอบอาคารที่ว่าการอำเภอเมืองนครราชสีมา ตำบลในเมือง อำเภอเมืองนครราชสีมา จังหวัดนครราชสีมา ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>★ (รถเข็น)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=63c26320-0a57-49c2-b838-a56d90ad3d33</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=185a0dfc-62ed-4497-966a-c01f547f4cfe</t>
         </is>
       </c>
     </row>
@@ -2643,15 +2643,15 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>กรมการปกครอง</t>
+          <t>สำนักงานประกันสังคม</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1503</v>
+        <v>1706</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ประกอบอาคารที่ว่าการอำเภอเมืองนครราชสีมา ตำบลในเมือง อำเภอเมืองนครราชสีมา จังหวัดนครราชสีมา ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง จำนวน 1 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=185a0dfc-62ed-4497-966a-c01f547f4cfe</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b01336ca-7547-423f-beb5-e3a81696e22b</t>
         </is>
       </c>
     </row>
@@ -2678,15 +2678,15 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>สำนักงานประกันสังคม</t>
+          <t>สำนักงานพัฒนาวิทยาศาสตร์และเทคโนโลยีแห่งชาติ</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1706</v>
+        <v>1905</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง จำนวน 1 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อระบบครุภัณฑ์สนับสนุนการพัฒนาเศรษฐกิจชีวภาพ เศรษฐกิจหมุนเวียน และเศรษฐกิจสีเขียว ตำบลคลองหนึ่ง อำเภอคลองหลวง จังหวัดปทุมธานี 1 ระบบ เครื่องปั่นเหวี่ยงความเร็วสูง (Superspeed centrifuge) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2701,27 +2701,27 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b01336ca-7547-423f-beb5-e3a81696e22b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=359b6f0b-0eeb-4b7f-9d76-b98fb3fa120d</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>สำนักงานพัฒนาวิทยาศาสตร์และเทคโนโลยีแห่งชาติ</t>
+          <t>ศูนย์อำนวยการรักษาผลประโยชน์ของชาติทางทะเล</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1905</v>
+        <v>138</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อระบบครุภัณฑ์สนับสนุนการพัฒนาเศรษฐกิจชีวภาพ เศรษฐกิจหมุนเวียน และเศรษฐกิจสีเขียว ตำบลคลองหนึ่ง อำเภอคลองหลวง จังหวัดปทุมธานี 1 ระบบ เครื่องปั่นเหวี่ยงความเร็วสูง (Superspeed centrifuge) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องคอมพิวเตอร์โน้ตบุ๊ก สำหรับงานประมวลผล จำนวน ๒๒ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2731,12 +2731,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, โน้ตบุ๊ก)</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=359b6f0b-0eeb-4b7f-9d76-b98fb3fa120d</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=809976d2-f842-4f28-993b-5dbf2627d012</t>
         </is>
       </c>
     </row>
@@ -2748,15 +2748,15 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ศูนย์อำนวยการรักษาผลประโยชน์ของชาติทางทะเล</t>
+          <t>สำนักงานปลัดกระทรวงกลาโหม</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>138</v>
+        <v>201</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องคอมพิวเตอร์โน้ตบุ๊ก สำหรับงานประมวลผล จำนวน ๒๒ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์แผนกแผนและโครงการ รบท.อท.ศอพท. จำนวน 5 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2766,12 +2766,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, โน้ตบุ๊ก)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=809976d2-f842-4f28-993b-5dbf2627d012</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=24573f9d-aa0a-45b1-91fc-930f70268f4e</t>
         </is>
       </c>
     </row>
@@ -2783,15 +2783,15 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงกลาโหม</t>
+          <t>กรมสรรพากร</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>201</v>
+        <v>307</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์แผนกแผนและโครงการ รบท.อท.ศอพท. จำนวน 5 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อวัสดุสิ้นเปลืองเพื่อใช้กับระบบเครื่องพิมพ์ต่อเนื่องความเร็วสูง เพื่อใช้สำหรับพิมพ์เอกสารทางภาษี ประจำปี พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2801,12 +2801,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (เครื่องพิมพ์)</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=24573f9d-aa0a-45b1-91fc-930f70268f4e</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c848bed5-5bad-40b5-8056-82b6f95bfae2</t>
         </is>
       </c>
     </row>
@@ -2818,15 +2818,15 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>กรมสรรพากร</t>
+          <t>กรมการข้าว</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>307</v>
+        <v>718</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการจัดซื้อวัสดุสิ้นเปลืองเพื่อใช้กับระบบเครื่องพิมพ์ต่อเนื่องความเร็วสูง เพื่อใช้สำหรับพิมพ์เอกสารทางภาษี ประจำปี พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การเกษตร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>★ (เครื่องพิมพ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c848bed5-5bad-40b5-8056-82b6f95bfae2</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8218601d-a676-42ae-849d-028704cbe916</t>
         </is>
       </c>
     </row>
@@ -2853,15 +2853,15 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>กรมการข้าว</t>
+          <t>กรมท่าอากาศยาน</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>718</v>
+        <v>805</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การเกษตร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างงานจ้างเหมาทำความสะอาดอาคารที่พักผู้โดยสาร และเก็บรถเข็นสัมภาระผู้โดยสารที่ท่าอากาศยานลำปาง ประจำปีงบประมาณ ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2871,12 +2871,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (รถเข็น)</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8218601d-a676-42ae-849d-028704cbe916</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=182d87d4-9f00-4361-9f26-bcf65839d3d5</t>
         </is>
       </c>
     </row>
@@ -2888,15 +2888,15 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>กรมท่าอากาศยาน</t>
+          <t>กรมโยธาธิการและผังเมือง</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>805</v>
+        <v>1507</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างงานจ้างเหมาทำความสะอาดอาคารที่พักผู้โดยสาร และเก็บรถเข็นสัมภาระผู้โดยสารที่ท่าอากาศยานลำปาง ประจำปีงบประมาณ ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างก่อสร้างโครงการก่อสร้างเขื่อนป้องกันตลิ่งริมแม่น้ำยม บ้านวังต้นเกลือ หมู่ที่ 7 ตำบลปากกาง อำเภอลอง จังหวัดแพร่ ความยาวไม่น้อยกว่า 1,000 เมตร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2906,32 +2906,32 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>★ (รถเข็น)</t>
+          <t>★ (ปากกา)</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=182d87d4-9f00-4361-9f26-bcf65839d3d5</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2815a715-ddfc-40d8-b3e8-78d6367955f5</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>กรมโยธาธิการและผังเมือง</t>
+          <t>สำนักงานเศรษฐกิจการคลัง</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1507</v>
+        <v>311</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างก่อสร้างโครงการก่อสร้างเขื่อนป้องกันตลิ่งริมแม่น้ำยม บ้านวังต้นเกลือ หมู่ที่ 7 ตำบลปากกาง อำเภอลอง จังหวัดแพร่ ความยาวไม่น้อยกว่า 1,000 เมตร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการต่ออายุ License ของซอฟต์แวร์ตรวจจับและตอบสนอง ต่อภัยคุกคามทางไซเบอร์ (Endpoint Detection and Response  EDR) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>★ (ปากกา)</t>
+          <t>★ (ซอฟต์แวร์)</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2815a715-ddfc-40d8-b3e8-78d6367955f5</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=94729b88-7aec-43e6-9dcb-0fd5f83cf536</t>
         </is>
       </c>
     </row>
@@ -2958,17 +2958,15 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>สำนักงานเศรษฐกิจการคลัง</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>0311</t>
-        </is>
+          <t>กรมส่งเสริมและพัฒนาคุณภาพชีวิตคนพิการ</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>607</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการต่ออายุ License ของซอฟต์แวร์ตรวจจับและตอบสนอง ต่อภัยคุกคามทางไซเบอร์ (Endpoint Detection and Response  EDR) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์งานบ้านงานครัวและครุภัณฑ์สำนักงาน จำนวน ๒๕ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2978,12 +2976,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>★ (ซอฟต์แวร์)</t>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=94729b88-7aec-43e6-9dcb-0fd5f83cf536</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=68659363-920b-4d6a-80fa-3d50e542f641</t>
         </is>
       </c>
     </row>
@@ -2995,17 +2993,15 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>กรมส่งเสริมและพัฒนาคุณภาพชีวิตคนพิการ</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>0607</t>
-        </is>
+          <t>กรมการข้าว</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>718</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์งานบ้านงานครัวและครุภัณฑ์สำนักงาน จำนวน ๒๕ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -3015,12 +3011,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=68659363-920b-4d6a-80fa-3d50e542f641</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c5b19896-e529-4c05-a497-b6f318a91a77</t>
         </is>
       </c>
     </row>
@@ -3032,17 +3028,15 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>กรมการข้าว</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>0718</t>
-        </is>
+          <t>กรมท่าอากาศยาน</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>805</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาทำความสะอาดที่พักผู้โดยสาร รวมทั้งอาคารต่าง ๆ และเก็บรถเข็นสัมภาระผู้โดยสาร ที่ท่าอากาศยานสุราษฎร์ธานี ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -3052,12 +3046,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (รถเข็น)</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c5b19896-e529-4c05-a497-b6f318a91a77</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=772b1ba1-dc6a-4f2c-ad6a-7b9398a81899</t>
         </is>
       </c>
     </row>
@@ -3069,17 +3063,15 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>กรมท่าอากาศยาน</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>0805</t>
-        </is>
+          <t>กรมทางหลวง</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>806</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาทำความสะอาดที่พักผู้โดยสาร รวมทั้งอาคารต่าง ๆ และเก็บรถเข็นสัมภาระผู้โดยสาร ที่ท่าอากาศยานสุราษฎร์ธานี ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างงานจ้างเหมาบริหารจัดการระบบควบคุมการอำนวยการจราจรด้านความปลอดภัยศูนย์บริหารจัดการจราจรกลางมอเตอร์เวย์ (Traffic Management Center) ลาดกระบังและพัทยา พร้อมปรับปรุงโปรแกรมระบบเพื่อรองรับความต้องการของผู้ใช้งานเพิ่มเติม ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -3089,12 +3081,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>★ (รถเข็น)</t>
+          <t>★ (มอเตอร์)</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=772b1ba1-dc6a-4f2c-ad6a-7b9398a81899</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a5144693-ef25-4928-be3e-49b03193e74c</t>
         </is>
       </c>
     </row>
@@ -3106,17 +3098,15 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>กรมทางหลวง</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>0806</t>
-        </is>
+          <t>กรมที่ดิน</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>1505</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างงานจ้างเหมาบริหารจัดการระบบควบคุมการอำนวยการจราจรด้านความปลอดภัยศูนย์บริหารจัดการจราจรกลางมอเตอร์เวย์ (Traffic Management Center) ลาดกระบังและพัทยา พร้อมปรับปรุงโปรแกรมระบบเพื่อรองรับความต้องการของผู้ใช้งานเพิ่มเติม ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อวัสดุหมึกพิมพ์ จำนวน ๓๖ รายการ สำหรับใช้ในราชการกองเทคโนโลยีทำแผนที่ ประจำปีงบประมาณ พ.ศ. ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -3126,12 +3116,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>★ (มอเตอร์)</t>
+          <t>★ (หมึกพิมพ์)</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a5144693-ef25-4928-be3e-49b03193e74c</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=aabc5e98-123d-4aca-81d1-decdb50fe286</t>
         </is>
       </c>
     </row>
@@ -3143,17 +3133,15 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>กรมที่ดิน</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>1505</t>
-        </is>
+          <t>สำนักงานพัฒนาเทคโนโลยีอวกาศและภูมิสารสนเทศ (องค์การมหาชน)</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>1906</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อวัสดุหมึกพิมพ์ จำนวน ๓๖ รายการ สำหรับใช้ในราชการกองเทคโนโลยีทำแผนที่ ประจำปีงบประมาณ พ.ศ. ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์คอมพิวเตอร์และอุปกรณ์ต่อพ่วงสำหรับการบริการข้อมูลดาวเทียม ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3163,12 +3151,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>★ (หมึกพิมพ์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=aabc5e98-123d-4aca-81d1-decdb50fe286</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a78cc797-5c4c-405a-8950-d7cf8b14e796</t>
         </is>
       </c>
     </row>
@@ -3180,17 +3168,15 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>สำนักงานพัฒนาเทคโนโลยีอวกาศและภูมิสารสนเทศ (องค์การมหาชน)</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>1906</t>
-        </is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>2102</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์คอมพิวเตอร์และอุปกรณ์ต่อพ่วงสำหรับการบริการข้อมูลดาวเทียม ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง รายการรถพยาบาลพร้อมอุปกรณ์ช่วยชีวิตขั้นสูง จำนวน 2 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3200,34 +3186,34 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a78cc797-5c4c-405a-8950-d7cf8b14e796</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=141cb2cf-43e6-4593-806a-e73fbfa47ecf</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กองทัพบก</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2102</t>
+          <t>0204</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง รายการรถพยาบาลพร้อมอุปกรณ์ช่วยชีวิตขั้นสูง จำนวน 2 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อวัสดุอุปกรณ์และเคมีภัณฑ์ เพื่อสนับสนุนงานผลิตกระสุนปืนเล็ก ขนาด 5.56 มิลลิเมตร ชนิดธรรมดามีแกนเหล็ก M855 (กล่องกระดาษบรรจุ กระสุนปืนเล็กฯ และอื่นๆ) รวม 25 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3237,12 +3223,419 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
+          <t>★ (กระดาษ)</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1d2377e0-663a-4e8b-9882-8ab158aaf678</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>กรมส่งเสริมและพัฒนาคุณภาพชีวิตคนพิการ</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>0607</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อเครื่องปรับอากาศแบบแยกส่วน ๓๐๐๐๐ บีทียู จากกองทุนส่งเสริมและพัฒนาคุณภาพชีวิตคนพิการ ประจำปีงบประมาณ ๒๕๖๙ (ครั้งที่ ๒) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>★ (เครื่องปรับอากาศ)</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=142cdcf4-2922-405e-9aee-af99f49d0e7b</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>กรมส่งเสริมการเกษตร</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>0711</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างเหมาบริการดูแลและบำรุงรักษาระบบควบคุมทราฟฟิกเครือข่ายคอมพิวเตอร์ ประจำปีงบประมาณ พ.ศ. 2570 ระยะเวลา 12 เดือน (ตั้งแต่วันที่ 1 ตุลาคม 2569 - 30 กันยายน 2570) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=cdcb45f4-9ae8-4ec9-af99-fb23527e1d3b</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>กรมการข้าว</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>0718</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์ประจำคลังเมล็ดพันธุ์ แขวงลาดยาว เขตจตุจักร กรุงเทพมหานคร จำนวน ๖ ชุด ครั้งที่ ๔ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
           <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=141cb2cf-43e6-4593-806a-e73fbfa47ecf</t>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8208cc5a-0a8b-4da2-af87-9184c6e521f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>กรมท่าอากาศยาน</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างจ้างเหมาทำความสะอาดอาคารที่พักผู้โดยสาร รวมทั้งอาคารทำการต่าง ๆ และเก็บรถเข็นสัมภาระผู้โดยสารท่าอากาศยานร้อยเอ็ด ประจำปีงบประมาณ 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>★ (รถเข็น)</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c9704867-793e-4e95-88cf-1bcb2c5caa23</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>กรมทางหลวง</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>0806</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้องานจัดซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 4 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4f518da9-2bb6-4c9c-a955-d80e84cccad6</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>กรมสวัสดิการและคุ้มครองแรงงาน</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>1705</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อซื้อครุภัณฑ์สำนักงาน เครื่องปรับอากาศทดแทน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์, เครื่องปรับอากาศ)</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8a07f87d-952b-4390-beab-11a825700ee1</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>สำนักงานพัฒนาวิทยาศาสตร์และเทคโนโลยีแห่งชาติ</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>1905</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างเหมาพนักงานรักษาความปลอดภัย เขตอุตสาหกรรมซอฟต์แวร์ประเทศไทย อาคารซอฟต์แวร์พาร์ค ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>★ (ซอฟต์แวร์)</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6309e067-a689-48f0-8eb1-2fbd31fe58fa</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>สำนักงานพัฒนาวิทยาศาสตร์และเทคโนโลยีแห่งชาติ</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>1905</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อสิทธิการใช้ซอฟต์แวร์ป้องกันไวรัส ปี 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>★ (ซอฟต์แวร์)</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e17c4ba8-b903-445f-9b55-025a1eda709d</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>สำนักงานคณะกรรมการอาหารและยา</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2110</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างบำรุงรักษาเครื่องปรับอากาศของอาคาร ๑-๗ และเครื่องปรับอากาศอาคาร ๘ (ระบบ VRV) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>★ (เครื่องปรับอากาศ)</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b07375fb-63e3-4297-bf8e-e012475dd2c8</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>สำนักงานคณะกรรมการอาหารและยา</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2110</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อการจัดหาครุภัณฑ์เพื่อจัดทำห้องศูนย์ปฏิบัติการเฝ้าระวังความมั่นคงปลอดภัยไซเบอร์ (SOC) และห้อง War Room (FDACERT) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=47dd02cc-31a8-4b5a-b8c4-07c1805a94e4</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>สถาบันพระบรมราชชนก</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2117</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การศึกษา (หุ่น จำนวน ๗ รายการ) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3b4c51a5-0c4c-4c70-8a3d-801831b0f4e2</t>
         </is>
       </c>
     </row>

--- a/Backup/eGP_Monthly_Main_202608.xlsx
+++ b/Backup/eGP_Monthly_Main_202608.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G91"/>
+  <dimension ref="A1:G102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3206,10 +3206,8 @@
           <t>กองทัพบก</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>0204</t>
-        </is>
+      <c r="C80" t="n">
+        <v>204</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -3243,10 +3241,8 @@
           <t>กรมส่งเสริมและพัฒนาคุณภาพชีวิตคนพิการ</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>0607</t>
-        </is>
+      <c r="C81" t="n">
+        <v>607</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -3280,10 +3276,8 @@
           <t>กรมส่งเสริมการเกษตร</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>0711</t>
-        </is>
+      <c r="C82" t="n">
+        <v>711</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -3317,10 +3311,8 @@
           <t>กรมการข้าว</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>0718</t>
-        </is>
+      <c r="C83" t="n">
+        <v>718</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -3354,10 +3346,8 @@
           <t>กรมท่าอากาศยาน</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>0805</t>
-        </is>
+      <c r="C84" t="n">
+        <v>805</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -3391,10 +3381,8 @@
           <t>กรมทางหลวง</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>0806</t>
-        </is>
+      <c r="C85" t="n">
+        <v>806</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -3428,10 +3416,8 @@
           <t>กรมสวัสดิการและคุ้มครองแรงงาน</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>1705</t>
-        </is>
+      <c r="C86" t="n">
+        <v>1705</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -3465,10 +3451,8 @@
           <t>สำนักงานพัฒนาวิทยาศาสตร์และเทคโนโลยีแห่งชาติ</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>1905</t>
-        </is>
+      <c r="C87" t="n">
+        <v>1905</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -3502,10 +3486,8 @@
           <t>สำนักงานพัฒนาวิทยาศาสตร์และเทคโนโลยีแห่งชาติ</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>1905</t>
-        </is>
+      <c r="C88" t="n">
+        <v>1905</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -3539,10 +3521,8 @@
           <t>สำนักงานคณะกรรมการอาหารและยา</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>2110</t>
-        </is>
+      <c r="C89" t="n">
+        <v>2110</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -3576,10 +3556,8 @@
           <t>สำนักงานคณะกรรมการอาหารและยา</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>2110</t>
-        </is>
+      <c r="C90" t="n">
+        <v>2110</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -3613,10 +3591,8 @@
           <t>สถาบันพระบรมราชชนก</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>2117</t>
-        </is>
+      <c r="C91" t="n">
+        <v>2117</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -3636,6 +3612,413 @@
       <c r="G91" t="inlineStr">
         <is>
           <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3b4c51a5-0c4c-4c70-8a3d-801831b0f4e2</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>กรมศุลกากร</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>0305</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างบริการบำรุงรักษาและซ่อมแซมแก้ไขคอมพิวเตอร์ อุปกรณ์การประมวลผลและระบบคอมพิวเตอร์ โครงการจัดหาระบบคอมพิวเตอร์ศุลกากรเพื่อการเชื่อมโยงข้อมูลอิเล็กทรอนิกส์ ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4503910f-f2ae-4227-b47b-48df453f0a93</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>กรมศุลกากร</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>0305</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างบริการบำรุงรักษาและซ่อมแซมแก้ไขคอมพิวเตอร์ อุปกรณ์การประมวลผลและระบบคอมพิวเตอร์ โครงการปรับปรุงระบบ ebXML Gateway เพื่อรองรับการให้บริการศุลกากรอิเล็กทรอนิกส์ ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ce3d73bf-bb6c-4a99-acca-ff44183511cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>กรมศุลกากร</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>0305</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างจ้างบริการบำรุงรักษาและซ่อมแซมแก้ไขคอมพิวเตอร์ อุปกรณ์การประมวลผลและระบบคอมพิวเตอร์ โครงการอุปกรณ์สนับสนุนการทำงานของศูนย์คอมพิวเตอร์กรมศุลกากร ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7775b534-ea03-4ffb-ac5d-90c7db6bc7b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>กรมศุลกากร</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>0305</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างบริการบำรุงรักษาและซ่อมแซมแก้ไขคอมพิวเตอร์ อุปกรณ์การประมวลผลและระบบคอมพิวเตอร์ โครงการศูนย์คอมพิวเตอร์สำรองกรมศุลกากร ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1879e83a-144e-423d-b532-f2cd8290ea08</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงการต่างประเทศ</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อเครื่องทำลายเอกสาร จำนวน ๓ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>★ (เครื่องทำลายเอกสาร)</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=5aa9afaa-ee7a-4e12-a007-c1a2e70fca14</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>กรมชลประทาน</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>0703</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อเครื่องสูบน้ำชนิดหอยโข่งแบบเพลาตั้งขับด้วยมอเตอร์ไฟฟ้า สำหรับตัวเรือนทำจากคอนกรีต อัตราการสูบน้ำ 25 ลูกบาศก์เมตรต่อวินาที ระยะยกน้ำ 14.7 เมตร พร้อมอุปกรณ์ประกอบ สำหรับงานปรับปรุงสถานีสูบน้ำสุวรรณภูมิ ตำบลบางปู อำเภอเมืองสมุทรปราการ จังหวัดสมุทรปราการ ระยะ 2 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>★ (มอเตอร์)</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=be815b3b-e3d7-446b-a206-6ad4f209a8c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>กรมทางหลวง</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>0806</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างงานจ้างเหมาบำรุงรักษาเครื่องปรับอากาศ เครื่องฟอกอากาศ บนทางหลวงพิเศษหมายเลข 7 และหมายเลข 9 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>★ (เครื่องปรับอากาศ, เครื่องฟอกอากาศ)</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=69859198-9edc-48f8-91cc-632c43362ddd</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>สำนักงานคณะกรรมการกำกับกิจการพลังงาน</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>1208</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างบริการดูแลระบบเครื่องแม่ข่ายและระบบฐานข้อมูล ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>★ (เครื่องแม่ข่าย)</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e583d715-8b49-4769-b85c-5039a857558b</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>กรมพัฒนาฝีมือแรงงาน</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>1704</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์สำนักงาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ace2f93e-9dcb-4791-89cb-eb69e8c6ed95</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>สถาบันมาตรวิทยาแห่งชาติ</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>1907</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>ประกวดราคาเช่างานจ้างเหมาเช่าเครื่องถ่ายเอกสารพร้อมกระดาษ ประจำปีงบประมาณ พ.ศ. 2570 (ครั้งที่ 2) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>★ (กระดาษ)</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=181ceb24-015e-4355-b3ce-c52435a2ebf3</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อขออนุมัติจัดซื้อครุภัณฑ์การแพทย์ จำนวน ๔ รายการ โรงพยาบาลส่งเสริมสุขภาพตำบลบ้านสุเหร่าแดง ต.ละหาร งบค่าเสื่อม ปีงบประมาณ ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=273a0bc0-d4de-437f-9c1b-bc3a31e64d06</t>
         </is>
       </c>
     </row>

--- a/Backup/eGP_Monthly_Main_202608.xlsx
+++ b/Backup/eGP_Monthly_Main_202608.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G102"/>
+  <dimension ref="A1:G113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3626,10 +3626,8 @@
           <t>กรมศุลกากร</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>0305</t>
-        </is>
+      <c r="C92" t="n">
+        <v>305</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -3663,10 +3661,8 @@
           <t>กรมศุลกากร</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>0305</t>
-        </is>
+      <c r="C93" t="n">
+        <v>305</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -3700,10 +3696,8 @@
           <t>กรมศุลกากร</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>0305</t>
-        </is>
+      <c r="C94" t="n">
+        <v>305</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -3737,10 +3731,8 @@
           <t>กรมศุลกากร</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>0305</t>
-        </is>
+      <c r="C95" t="n">
+        <v>305</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -3774,10 +3766,8 @@
           <t>สำนักงานปลัดกระทรวงการต่างประเทศ</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>0402</t>
-        </is>
+      <c r="C96" t="n">
+        <v>402</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -3811,10 +3801,8 @@
           <t>กรมชลประทาน</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>0703</t>
-        </is>
+      <c r="C97" t="n">
+        <v>703</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -3848,10 +3836,8 @@
           <t>กรมทางหลวง</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>0806</t>
-        </is>
+      <c r="C98" t="n">
+        <v>806</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -3885,10 +3871,8 @@
           <t>สำนักงานคณะกรรมการกำกับกิจการพลังงาน</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>1208</t>
-        </is>
+      <c r="C99" t="n">
+        <v>1208</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -3922,10 +3906,8 @@
           <t>กรมพัฒนาฝีมือแรงงาน</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>1704</t>
-        </is>
+      <c r="C100" t="n">
+        <v>1704</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -3959,10 +3941,8 @@
           <t>สถาบันมาตรวิทยาแห่งชาติ</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>1907</t>
-        </is>
+      <c r="C101" t="n">
+        <v>1907</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -3996,29 +3976,434 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
+      <c r="C102" t="n">
+        <v>2102</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อขออนุมัติจัดซื้อครุภัณฑ์การแพทย์ จำนวน ๔ รายการ โรงพยาบาลส่งเสริมสุขภาพตำบลบ้านสุเหร่าแดง ต.ละหาร งบค่าเสื่อม ปีงบประมาณ ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=273a0bc0-d4de-437f-9c1b-bc3a31e64d06</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>สำนักงานกองทุนสนับสนุนการสร้างเสริมสุขภาพ</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>0117</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อคอมพิวเตอร์พกพา (Notebook) เพื่อใช้ในงานสำนักงาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, คอมพิวเตอร์พกพา)</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d6061e25-bdb7-4047-bea2-87696e3906ec</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงการพัฒนาสังคมและความมั่นคงของมนุษย์</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>0602</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างบำรุงรักษาซ่อมแซมแก้ไขเครื่องคอมพิวเตอร์แม่ข่าย ระบบฐานข้อมูลระบบเครือข่ายคอมพิวเตอร์และอุปกรณ์ สป.พม. จำนวน 97 หน่วยงาน ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=29143bc7-9255-41e4-b1ac-b83faf86e47f</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>กรมท่าอากาศยาน</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างเหมาทำความสะอาดอาคารที่พักผู้โดยสารรวมทั้งอาคารทำการต่างๆ  และเก็บรถเข็นสัมภาระผู้โดยสาร ที่ท่าอากาศยานบุรีรัมย์ ประจำปีงบประมาณ 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>★ (รถเข็น)</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3ae485a6-87df-4b60-b093-5ff12ede2ad4</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>กรมท่าอากาศยาน</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างเหมาทำความสะอาดอาคารผู้โดยสารหลังที่ 1 หลังที่ 2 รวมทั้งอาคารทำการต่างๆ และเก็บรถเข็นสัมภาระผู้โดยสาร ที่ท่าอากาศยานบุรีรัมย์ ประจำปีงบประมาณ 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>★ (รถเข็น)</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=25b919c3-ecbe-4fdb-9705-ca375467100a</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>กรมอุทยานแห่งชาติ สัตว์ป่า และพันธุ์พืช</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>0909</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างจ้างเหมาบำรุงรักษาระบบงานบนเครือข่ายคอมพิวเตอร์ทั้งระบบ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=5e084c4c-aa21-4b51-a79a-465c5de119bc</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>กรมการปกครอง</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>1503</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ประกอบอาคารที่ว่าการอำเภอเมืองนครราชสีมา  ตำบลในเมือง อำเภอเมืองนครราชสีมา จังหวัดนครราชสีมา  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f7fdea88-1922-4aff-8aa2-4cb97ab2e8d5</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>กรมที่ดิน</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>1505</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบรับเรื่องร้องเรียนร้องทุกข์ผ่านเว็บไซต์ศูนย์ดำรงธรรมกรมที่ดินและระบบรับเรื่องร้องเรียนร้องทุกข์และให้คำปรึกษาผ่าน Mobile และซอฟต์แวร์ระบบจดหมายอิเล็กทรอนิกส์ ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>★ (ซอฟต์แวร์)</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=eb62e9eb-50f1-40a6-9530-a8f0b4f340ac</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>กรมการศาสนา</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>1803</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อจัดซื้อหมึกเครื่องพิมพ์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>★ (หมึกเครื่องพิมพ์, เครื่องพิมพ์)</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=60258dc2-92c9-4dcc-8a7d-832aee55d3aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
         <is>
           <t>2102</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>ประกวดราคาซื้อขออนุมัติจัดซื้อครุภัณฑ์การแพทย์ จำนวน ๔ รายการ โรงพยาบาลส่งเสริมสุขภาพตำบลบ้านสุเหร่าแดง ต.ละหาร งบค่าเสื่อม ปีงบประมาณ ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>ไม่ระบุ</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องตรวจคลื่นไฟฟ้าหัวใจ พร้อมระบบวิเคราะห์ผล และจัดเก็บภาพในระบบเครือข่าย จำนวน 8 เครื่อง งบประมาณกองสลากการกุศลในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจาก สถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
         <is>
           <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=273a0bc0-d4de-437f-9c1b-bc3a31e64d06</t>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=066f19c9-997c-4c89-8e66-f0ea73fbd555</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องตรวจอวัยวะภายในด้วยคลื่นเสียงความถี่สูงแบบพกพาไม่ต้องชาร์จไฟฟ้าพร้อมระบบแพทย์ทางไกล จำนวน 6 เครื่อง งบประมาณกองสลากการกุศลในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=474cdfd4-81a1-4e4e-a157-21ba990bf7aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>สถาบันพระบรมราชชนก</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>2117</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 8 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d1d5db2e-9c81-4269-9c77-d4fe6a048d46</t>
         </is>
       </c>
     </row>

--- a/Backup/eGP_Monthly_Main_202608.xlsx
+++ b/Backup/eGP_Monthly_Main_202608.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G113"/>
+  <dimension ref="A1:G124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4011,10 +4011,8 @@
           <t>สำนักงานกองทุนสนับสนุนการสร้างเสริมสุขภาพ</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>0117</t>
-        </is>
+      <c r="C103" t="n">
+        <v>117</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -4048,10 +4046,8 @@
           <t>สำนักงานปลัดกระทรวงการพัฒนาสังคมและความมั่นคงของมนุษย์</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>0602</t>
-        </is>
+      <c r="C104" t="n">
+        <v>602</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -4085,10 +4081,8 @@
           <t>กรมท่าอากาศยาน</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>0805</t>
-        </is>
+      <c r="C105" t="n">
+        <v>805</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -4122,10 +4116,8 @@
           <t>กรมท่าอากาศยาน</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>0805</t>
-        </is>
+      <c r="C106" t="n">
+        <v>805</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -4159,10 +4151,8 @@
           <t>กรมอุทยานแห่งชาติ สัตว์ป่า และพันธุ์พืช</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>0909</t>
-        </is>
+      <c r="C107" t="n">
+        <v>909</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -4196,10 +4186,8 @@
           <t>กรมการปกครอง</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>1503</t>
-        </is>
+      <c r="C108" t="n">
+        <v>1503</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -4233,10 +4221,8 @@
           <t>กรมที่ดิน</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>1505</t>
-        </is>
+      <c r="C109" t="n">
+        <v>1505</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -4270,10 +4256,8 @@
           <t>กรมการศาสนา</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>1803</t>
-        </is>
+      <c r="C110" t="n">
+        <v>1803</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -4307,10 +4291,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C111" t="n">
+        <v>2102</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -4344,10 +4326,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C112" t="n">
+        <v>2102</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -4381,10 +4361,8 @@
           <t>สถาบันพระบรมราชชนก</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>2117</t>
-        </is>
+      <c r="C113" t="n">
+        <v>2117</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -4404,6 +4382,413 @@
       <c r="G113" t="inlineStr">
         <is>
           <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d1d5db2e-9c81-4269-9c77-d4fe6a048d46</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>กองทัพบก</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>0204</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อน้ำยาทำความสะอาดและปรนนิบัติบำรุงยุทโธปกรณ์อาวุธปืน (ขนาดบรรจุ ๑ แกลลอน) จำนวน ๑,๒๓๖ แกลลอน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>★ (น้ำยาทำความสะอาด)</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d496fc56-461e-483f-8f7d-7208293810c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงการพัฒนาสังคมและความมั่นคงของมนุษย์</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>0602</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างบำรุงรักษาซ่อมแซมแก้ไขเครื่องคอมพิวเตอร์พร้อมโปรแกรม อุปกรณ์คอมพิวเตอร์และโสตทัศนูปกรณ์ (ส่วนกลาง) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b7d78b5f-e8d5-46e6-962e-742565711d09</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>กรมการขนส่งทางบก</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>0804</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาและซ่อมแซมแก้ไขอุปกรณ์คอมพิวเตอร์และระบบงานใบอนุญาตประกอบการขนส่งอิเล็กทรอนิกส์ (DLT E-Transport License  ETL) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=cbdda49e-2493-4b51-9c63-907c3926d6ce</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>กรมท่าอากาศยาน</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างเหมาทำความสะอาดอาคารที่พักผู้โดยสารรวมทั้งอาคารทำการต่างๆ และเก็บรถเข็นสัมภาระผู้โดยสารภายในท่าอากาศยานกระบี่ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>★ (รถเข็น)</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=5266af76-8720-464b-b0a2-da6898b534b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>กรมทรัพยากรน้ำบาดาล</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>0907</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบเครือข่ายคอมพิวเตอร์การสื่อสารประจำปีงบประมาณ พ.ศ. ๒๕๗๐ จำนวน ๑ ระบบ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a44ed71a-5fe0-4a83-be65-1e0d96f7bfac</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>กรมที่ดิน</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>1505</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อวัสดุคอมพิวเตอร์ (หมึกพิมพ์) สำหรับใช้ในราชการฝ่ายรังวัด สำนักงานที่ดินจังหวัดนครราชสีมา และสาขา ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>★ (หมึกพิมพ์, คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4644dfae-40c4-4413-a8b6-b049ac21ce1d</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>กรมบังคับคดี</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>1605</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างจ้างบริการดูแลบำรุงรักษาเครื่องปรับอากาศของกรมบังคับคดี ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>★ (เครื่องปรับอากาศ)</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=305436a7-b236-4fe7-bd03-3e537c1c8e26</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>สำนักงานพัฒนาวิทยาศาสตร์และเทคโนโลยีแห่งชาติ</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>1905</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>ประกวดราคาเช่าเครื่องคอมพิวเตอร์และอุปกรณ์คอมพิวเตอร์ ครั้งที่ 1/2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6d8dcfd8-3ac8-4960-8564-7544344ff0e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องเอกซเรย์เคลื่อนที่ระบบแพทย์ทางไกลแบบพกพาพร้อมชุดรับสัญญาณภาพดิจิตอลแบบไร้สาย จำนวน 2 เครื่อง งบประมาณกองสลากการกุศลในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=defa9a29-2b36-481a-8ef5-2a9de972b5f8</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องช่วยหายใจชนิดควบคุมด้วยปริมาตรและความดัน ขนาดกลาง จำนวน 4 เครื่อง งบประมาณกองสลากการกุศลในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a564f779-2ff3-4ee9-81b3-2060cb1c836f</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องผลิตออกซิเจนขนาด 10 ลิตร ของโรงพยาบาลชุมชน 8 แห่ง, โรงพยาบาลส่งเสริมสุขภาพตำบล 18 แห่ง และสถานีอนามัยเฉลิมพระเกียรติฯบ้านรุน จำนวน 66 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=94760102-19e3-4e13-841f-5b3f70698c80</t>
         </is>
       </c>
     </row>

--- a/Backup/eGP_Monthly_Main_202608.xlsx
+++ b/Backup/eGP_Monthly_Main_202608.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G124"/>
+  <dimension ref="A1:G135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4396,10 +4396,8 @@
           <t>กองทัพบก</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>0204</t>
-        </is>
+      <c r="C114" t="n">
+        <v>204</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -4433,10 +4431,8 @@
           <t>สำนักงานปลัดกระทรวงการพัฒนาสังคมและความมั่นคงของมนุษย์</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>0602</t>
-        </is>
+      <c r="C115" t="n">
+        <v>602</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -4470,10 +4466,8 @@
           <t>กรมการขนส่งทางบก</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>0804</t>
-        </is>
+      <c r="C116" t="n">
+        <v>804</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -4507,10 +4501,8 @@
           <t>กรมท่าอากาศยาน</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>0805</t>
-        </is>
+      <c r="C117" t="n">
+        <v>805</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -4544,10 +4536,8 @@
           <t>กรมทรัพยากรน้ำบาดาล</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>0907</t>
-        </is>
+      <c r="C118" t="n">
+        <v>907</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -4581,10 +4571,8 @@
           <t>กรมที่ดิน</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>1505</t>
-        </is>
+      <c r="C119" t="n">
+        <v>1505</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -4618,10 +4606,8 @@
           <t>กรมบังคับคดี</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>1605</t>
-        </is>
+      <c r="C120" t="n">
+        <v>1605</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -4655,10 +4641,8 @@
           <t>สำนักงานพัฒนาวิทยาศาสตร์และเทคโนโลยีแห่งชาติ</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>1905</t>
-        </is>
+      <c r="C121" t="n">
+        <v>1905</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -4692,10 +4676,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C122" t="n">
+        <v>2102</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -4729,10 +4711,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C123" t="n">
+        <v>2102</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -4766,29 +4746,434 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr">
+      <c r="C124" t="n">
+        <v>2102</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องผลิตออกซิเจนขนาด 10 ลิตร ของโรงพยาบาลชุมชน 8 แห่ง, โรงพยาบาลส่งเสริมสุขภาพตำบล 18 แห่ง และสถานีอนามัยเฉลิมพระเกียรติฯบ้านรุน จำนวน 66 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=94760102-19e3-4e13-841f-5b3f70698c80</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>กองทัพบก</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>0204</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์ประจำอาคาร จำนวน 7 รายการ เพื่อใช้ในงานปรับปรุงอาคารของ กรมทหารม้าที่ 1 รักษาพระองค์ (กองร้อยสนับสนุนส่วนหน้าที่ 1 กองพันซ่อมบำรุง กรมสนับสนุนที่ 12) เป็นโรงเรียนหน่วยเฉพาะกิจทหารมหาดเล็กรักษาพระองค์ 904 เป็นแผนงานเพิ่มเติมระหว่างปีงบประมาณ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e3357a33-4141-451a-ba12-43613540ff93</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>กองทัพเรือ</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>0205</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างเหมาบริการดูแลรักษาและซ่อมบำรุงระบบกล้องวงจรปิด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>★ (กล้องวงจรปิด)</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=dffca1b8-3974-493b-96f7-0266966337be</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงเกษตรและสหกรณ์</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>0702</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อซื้อวัสดุคอมพิวเตอร์ จำนวน 17 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=436e4fef-74b4-4218-9d53-178994df8d95</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>0704</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อประกวดราคาซื้อการจัดซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุก (ดีเซล) ขนาด ๑ ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า ๒,๔๐๐ ซีซี. หรือ กำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า ๑๑๐ กิโลวัตต์  ขับเคลื่อน ๒ ล้อ  แบบดับเบิ้ลแค็บ  พร้อมหลังคาไฟเบอร์กลาสหรือเหล็กหรือพลาสติกวิศวกรรม จำนวน ๑ คัน  ของสำนักงานตรวจบัญชีสหกรณ์ชลบุรี ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6dee1bac-977b-45a1-80ed-4156d6928072</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>กรมท่าอากาศยาน</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างบำรุงรักษาเครื่องแม่ข่ายคอมพิวเตอร์ HCI ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, เครื่องแม่ข่าย)</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=451c34a7-8037-4b6c-8435-e4a22cdec066</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>กรมทรัพยากรทางทะเลและชายฝั่ง</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>0904</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน ๕ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6511a18d-a968-4123-9bbf-9e02a1058f69</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>กรมป่าไม้</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>0912</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อเครื่องคอมพิวเตอร์โน้ตบุ๊ก สำหรับงานประมวลผล จำนวน ๓๘ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, โน้ตบุ๊ก)</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9c4c4c54-269c-4bc7-a38d-eefebbdeccc6</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>กรมป่าไม้</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>0912</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์ประจำศูนย์บัญชาการควบคุมไฟป่า จำนวน ๗ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=07513a33-2079-40d0-a3c7-4fcca2d0ae75</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามยาเสพติด</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>1611</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างเหมาบริการถ่ายเอกสารพร้อมเครื่องถ่ายเอกสาร กระดาษ วัสดุสิ้นเปลือง และพนักงานประจำเครื่องของสำนักงาน ป.ป.ส. ดินแดง สำนักงาน/ปปส.ทุ่งสองห้อง ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>★ (กระดาษ)</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=83ec0c0a-2690-4842-9b72-9b79a02041f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
         <is>
           <t>2102</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องผลิตออกซิเจนขนาด 10 ลิตร ของโรงพยาบาลชุมชน 8 แห่ง, โรงพยาบาลส่งเสริมสุขภาพตำบล 18 แห่ง และสถานีอนามัยเฉลิมพระเกียรติฯบ้านรุน จำนวน 66 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>ไม่ระบุ</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>★ (ครุภัณฑ์)</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=94760102-19e3-4e13-841f-5b3f70698c80</t>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อเครื่องกระตุกไฟฟ้าหัวใจชนิดอัตโนมัติ พร้อมตู้ตั้งพื้นจอแสดงผล และระบบสัญญาณเตือน ๓๒ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>★ (จอแสดงผล)</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=17e24d3e-9572-45f3-b487-c97291f7207b</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อเครื่องเอกซเรย์เคลื่อนที่ขนาด ไม่น้อยกว่า 300 mA.ขับเคลื่อนด้วยมอเตอร์ไฟฟ้า ๑ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>★ (มอเตอร์)</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7befad79-56d6-445b-9b45-c37447469898</t>
         </is>
       </c>
     </row>
